--- a/BOUTIQUE(2).xlsx
+++ b/BOUTIQUE(2).xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="89">
   <si>
     <t>DATE</t>
   </si>
@@ -634,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -703,6 +703,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1616,8 +1619,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau13456" displayName="Tableau13456" ref="C3:F103" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="C3:F103"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau13456" displayName="Tableau13456" ref="C3:F99" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="C3:F99"/>
   <tableColumns count="4">
     <tableColumn id="2" name="DATE" dataDxfId="7" dataCellStyle="Sortie"/>
     <tableColumn id="3" name="CONSOMMATION" dataDxfId="6" dataCellStyle="Sortie"/>
@@ -1923,20 +1926,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="36">
+      <c r="E1" s="39"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="37">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="2:9" s="2" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="36"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" spans="2:9" s="2" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
       <c r="C3" s="7" t="s">
@@ -1957,7 +1960,7 @@
       <c r="H3" s="21"/>
     </row>
     <row r="4" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>SUM(F4:F15)</f>
         <v>677</v>
       </c>
@@ -1979,7 +1982,7 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="5">
         <v>2</v>
       </c>
@@ -1995,7 +1998,7 @@
       <c r="G5" s="6"/>
     </row>
     <row r="6" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="5">
         <v>3</v>
       </c>
@@ -2011,7 +2014,7 @@
       <c r="G6" s="6"/>
     </row>
     <row r="7" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="5">
         <v>4</v>
       </c>
@@ -2028,7 +2031,7 @@
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="5">
         <v>5</v>
       </c>
@@ -2044,7 +2047,7 @@
       <c r="G8" s="6"/>
     </row>
     <row r="9" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="5">
         <v>6</v>
       </c>
@@ -2060,7 +2063,7 @@
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="5">
         <v>7</v>
       </c>
@@ -2076,7 +2079,7 @@
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="5">
         <v>8</v>
       </c>
@@ -2092,7 +2095,7 @@
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="5">
         <v>9</v>
       </c>
@@ -2108,7 +2111,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B13" s="34"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="5">
         <v>10</v>
       </c>
@@ -2124,7 +2127,7 @@
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B14" s="34"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="5">
         <v>11</v>
       </c>
@@ -2140,7 +2143,7 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B15" s="35"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="5">
         <v>12</v>
       </c>
@@ -2156,7 +2159,7 @@
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>SUM(F16:F26)</f>
         <v>795</v>
       </c>
@@ -2175,7 +2178,7 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B17" s="34"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="5">
         <v>2</v>
       </c>
@@ -2191,7 +2194,7 @@
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B18" s="34"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="5">
         <v>3</v>
       </c>
@@ -2207,7 +2210,7 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B19" s="34"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="5">
         <v>4</v>
       </c>
@@ -2223,7 +2226,7 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B20" s="34"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="5">
         <v>5</v>
       </c>
@@ -2239,7 +2242,7 @@
       <c r="G20" s="6"/>
     </row>
     <row r="21" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B21" s="34"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="10">
         <v>6</v>
       </c>
@@ -2255,7 +2258,7 @@
       <c r="G21" s="13"/>
     </row>
     <row r="22" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B22" s="34"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="10">
         <v>7</v>
       </c>
@@ -2271,7 +2274,7 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B23" s="34"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="10">
         <v>8</v>
       </c>
@@ -2287,7 +2290,7 @@
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B24" s="34"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="10">
         <v>9</v>
       </c>
@@ -2303,7 +2306,7 @@
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="10">
         <v>10</v>
       </c>
@@ -2319,7 +2322,7 @@
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B26" s="35"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="10">
         <v>11</v>
       </c>
@@ -2335,7 +2338,7 @@
       <c r="G26" s="6"/>
     </row>
     <row r="27" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B27" s="33">
+      <c r="B27" s="34">
         <f>SUM(F27:F35)</f>
         <v>490</v>
       </c>
@@ -2354,7 +2357,7 @@
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B28" s="34"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="5">
         <v>2</v>
       </c>
@@ -2370,7 +2373,7 @@
       <c r="G28" s="6"/>
     </row>
     <row r="29" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="5">
         <v>3</v>
       </c>
@@ -2386,7 +2389,7 @@
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B30" s="34"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="5">
         <v>4</v>
       </c>
@@ -2402,7 +2405,7 @@
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="5">
         <v>5</v>
       </c>
@@ -2418,7 +2421,7 @@
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="5">
         <v>6</v>
       </c>
@@ -2434,7 +2437,7 @@
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="5">
         <v>7</v>
       </c>
@@ -2450,7 +2453,7 @@
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="2:7" s="2" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="5">
         <v>8</v>
       </c>
@@ -2466,7 +2469,7 @@
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B35" s="35"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="5">
         <v>9</v>
       </c>
@@ -2482,7 +2485,7 @@
       <c r="G35" s="6"/>
     </row>
     <row r="36" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B36" s="33">
+      <c r="B36" s="34">
         <f>SUM(F36:F42)</f>
         <v>309</v>
       </c>
@@ -2501,7 +2504,7 @@
       <c r="G36" s="6"/>
     </row>
     <row r="37" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B37" s="34"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="5">
         <v>2</v>
       </c>
@@ -2517,7 +2520,7 @@
       <c r="G37" s="6"/>
     </row>
     <row r="38" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B38" s="34"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="5">
         <v>3</v>
       </c>
@@ -2533,7 +2536,7 @@
       <c r="G38" s="6"/>
     </row>
     <row r="39" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B39" s="34"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="5">
         <v>4</v>
       </c>
@@ -2549,7 +2552,7 @@
       <c r="G39" s="6"/>
     </row>
     <row r="40" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B40" s="34"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="5">
         <v>5</v>
       </c>
@@ -2565,7 +2568,7 @@
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B41" s="34"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="5">
         <v>6</v>
       </c>
@@ -2581,7 +2584,7 @@
       <c r="G41" s="6"/>
     </row>
     <row r="42" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B42" s="35"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="5">
         <v>7</v>
       </c>
@@ -2597,7 +2600,7 @@
       <c r="G42" s="6"/>
     </row>
     <row r="43" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B43" s="33">
+      <c r="B43" s="34">
         <f>SUM(F43:F49)</f>
         <v>324</v>
       </c>
@@ -2616,7 +2619,7 @@
       <c r="G43" s="6"/>
     </row>
     <row r="44" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B44" s="34"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="10">
         <v>2</v>
       </c>
@@ -2632,7 +2635,7 @@
       <c r="G44" s="17"/>
     </row>
     <row r="45" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B45" s="34"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="10">
         <v>3</v>
       </c>
@@ -2648,7 +2651,7 @@
       <c r="G45" s="17"/>
     </row>
     <row r="46" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B46" s="34"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="10">
         <v>4</v>
       </c>
@@ -2664,7 +2667,7 @@
       <c r="G46" s="17"/>
     </row>
     <row r="47" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B47" s="34"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="10">
         <v>5</v>
       </c>
@@ -2680,7 +2683,7 @@
       <c r="G47" s="17"/>
     </row>
     <row r="48" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B48" s="34"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="10">
         <v>6</v>
       </c>
@@ -2696,7 +2699,7 @@
       <c r="G48" s="17"/>
     </row>
     <row r="49" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B49" s="35"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="10">
         <v>7</v>
       </c>
@@ -2712,7 +2715,7 @@
       <c r="G49" s="17"/>
     </row>
     <row r="50" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B50" s="33">
+      <c r="B50" s="34">
         <f>SUM(F50:F58)</f>
         <v>405</v>
       </c>
@@ -2731,7 +2734,7 @@
       <c r="G50" s="17"/>
     </row>
     <row r="51" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B51" s="34"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="10">
         <v>2</v>
       </c>
@@ -2747,7 +2750,7 @@
       <c r="G51" s="17"/>
     </row>
     <row r="52" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B52" s="34"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="10">
         <v>3</v>
       </c>
@@ -2763,7 +2766,7 @@
       <c r="G52" s="17"/>
     </row>
     <row r="53" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B53" s="34"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="10">
         <v>4</v>
       </c>
@@ -2779,7 +2782,7 @@
       <c r="G53" s="17"/>
     </row>
     <row r="54" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B54" s="34"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="10">
         <v>5</v>
       </c>
@@ -2795,7 +2798,7 @@
       <c r="G54" s="17"/>
     </row>
     <row r="55" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B55" s="34"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="10">
         <v>6</v>
       </c>
@@ -2811,7 +2814,7 @@
       <c r="G55" s="17"/>
     </row>
     <row r="56" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B56" s="34"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="10">
         <v>7</v>
       </c>
@@ -2827,7 +2830,7 @@
       <c r="G56" s="17"/>
     </row>
     <row r="57" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B57" s="34"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="10">
         <v>8</v>
       </c>
@@ -2843,7 +2846,7 @@
       <c r="G57" s="17"/>
     </row>
     <row r="58" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B58" s="35"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="10">
         <v>9</v>
       </c>
@@ -2859,7 +2862,7 @@
       <c r="G58" s="17"/>
     </row>
     <row r="59" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B59" s="33">
+      <c r="B59" s="34">
         <f>SUM(F59:F65)</f>
         <v>439</v>
       </c>
@@ -2878,7 +2881,7 @@
       <c r="G59" s="17"/>
     </row>
     <row r="60" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B60" s="34"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="10">
         <v>2</v>
       </c>
@@ -2894,7 +2897,7 @@
       <c r="G60" s="17"/>
     </row>
     <row r="61" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B61" s="34"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="10">
         <v>3</v>
       </c>
@@ -2910,7 +2913,7 @@
       <c r="G61" s="17"/>
     </row>
     <row r="62" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B62" s="34"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="10">
         <v>4</v>
       </c>
@@ -2926,7 +2929,7 @@
       <c r="G62" s="17"/>
     </row>
     <row r="63" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B63" s="34"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="10">
         <v>5</v>
       </c>
@@ -2942,7 +2945,7 @@
       <c r="G63" s="17"/>
     </row>
     <row r="64" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B64" s="34"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="10">
         <v>6</v>
       </c>
@@ -2958,7 +2961,7 @@
       <c r="G64" s="17"/>
     </row>
     <row r="65" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B65" s="35"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="10">
         <v>7</v>
       </c>
@@ -2974,7 +2977,7 @@
       <c r="G65" s="17"/>
     </row>
     <row r="66" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B66" s="33">
+      <c r="B66" s="34">
         <f>SUM(F66:F72)</f>
         <v>316</v>
       </c>
@@ -2993,7 +2996,7 @@
       <c r="G66" s="17"/>
     </row>
     <row r="67" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B67" s="34"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="10">
         <v>2</v>
       </c>
@@ -3009,7 +3012,7 @@
       <c r="G67" s="17"/>
     </row>
     <row r="68" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B68" s="34"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="10">
         <v>3</v>
       </c>
@@ -3025,7 +3028,7 @@
       <c r="G68" s="17"/>
     </row>
     <row r="69" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B69" s="34"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="10">
         <v>4</v>
       </c>
@@ -3041,7 +3044,7 @@
       <c r="G69" s="17"/>
     </row>
     <row r="70" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B70" s="34"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="10">
         <v>5</v>
       </c>
@@ -3057,7 +3060,7 @@
       <c r="G70" s="17"/>
     </row>
     <row r="71" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B71" s="34"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="10">
         <v>6</v>
       </c>
@@ -3073,7 +3076,7 @@
       <c r="G71" s="17"/>
     </row>
     <row r="72" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B72" s="35"/>
+      <c r="B72" s="36"/>
       <c r="C72" s="10">
         <v>7</v>
       </c>
@@ -3089,7 +3092,7 @@
       <c r="G72" s="17"/>
     </row>
     <row r="73" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B73" s="33">
+      <c r="B73" s="34">
         <f>SUM(F73:F80)</f>
         <v>277</v>
       </c>
@@ -3108,7 +3111,7 @@
       <c r="G73" s="17"/>
     </row>
     <row r="74" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B74" s="34"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="10">
         <v>2</v>
       </c>
@@ -3124,7 +3127,7 @@
       <c r="G74" s="17"/>
     </row>
     <row r="75" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B75" s="34"/>
+      <c r="B75" s="35"/>
       <c r="C75" s="10">
         <v>3</v>
       </c>
@@ -3140,7 +3143,7 @@
       <c r="G75" s="17"/>
     </row>
     <row r="76" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B76" s="34"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="10">
         <v>4</v>
       </c>
@@ -3156,7 +3159,7 @@
       <c r="G76" s="17"/>
     </row>
     <row r="77" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B77" s="34"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="10">
         <v>5</v>
       </c>
@@ -3172,7 +3175,7 @@
       <c r="G77" s="17"/>
     </row>
     <row r="78" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B78" s="34"/>
+      <c r="B78" s="35"/>
       <c r="C78" s="10">
         <v>6</v>
       </c>
@@ -3188,7 +3191,7 @@
       <c r="G78" s="17"/>
     </row>
     <row r="79" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B79" s="34"/>
+      <c r="B79" s="35"/>
       <c r="C79" s="10">
         <v>7</v>
       </c>
@@ -3204,7 +3207,7 @@
       <c r="G79" s="17"/>
     </row>
     <row r="80" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B80" s="35"/>
+      <c r="B80" s="36"/>
       <c r="C80" s="10">
         <v>8</v>
       </c>
@@ -3220,7 +3223,7 @@
       <c r="G80" s="17"/>
     </row>
     <row r="81" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B81" s="33">
+      <c r="B81" s="34">
         <f>SUM(F81:F85)</f>
         <v>205</v>
       </c>
@@ -3239,7 +3242,7 @@
       <c r="G81" s="17"/>
     </row>
     <row r="82" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B82" s="34"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="10">
         <v>2</v>
       </c>
@@ -3255,7 +3258,7 @@
       <c r="G82" s="17"/>
     </row>
     <row r="83" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="10">
         <v>3</v>
       </c>
@@ -3271,7 +3274,7 @@
       <c r="G83" s="17"/>
     </row>
     <row r="84" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="10">
         <v>4</v>
       </c>
@@ -3287,7 +3290,7 @@
       <c r="G84" s="17"/>
     </row>
     <row r="85" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B85" s="35"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="10">
         <v>5</v>
       </c>
@@ -3303,7 +3306,7 @@
       <c r="G85" s="17"/>
     </row>
     <row r="86" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B86" s="33">
+      <c r="B86" s="34">
         <f>SUM(F86:F96)</f>
         <v>778</v>
       </c>
@@ -3322,7 +3325,7 @@
       <c r="G86" s="17"/>
     </row>
     <row r="87" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B87" s="34"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="10">
         <v>2</v>
       </c>
@@ -3338,7 +3341,7 @@
       <c r="G87" s="17"/>
     </row>
     <row r="88" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B88" s="34"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="10">
         <v>3</v>
       </c>
@@ -3354,7 +3357,7 @@
       <c r="G88" s="17"/>
     </row>
     <row r="89" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B89" s="34"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="10">
         <v>4</v>
       </c>
@@ -3370,7 +3373,7 @@
       <c r="G89" s="17"/>
     </row>
     <row r="90" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B90" s="34"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="10">
         <v>5</v>
       </c>
@@ -3386,7 +3389,7 @@
       <c r="G90" s="17"/>
     </row>
     <row r="91" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B91" s="34"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="10">
         <v>6</v>
       </c>
@@ -3402,7 +3405,7 @@
       <c r="G91" s="17"/>
     </row>
     <row r="92" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B92" s="34"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="10">
         <v>7</v>
       </c>
@@ -3418,7 +3421,7 @@
       <c r="G92" s="17"/>
     </row>
     <row r="93" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B93" s="34"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="10">
         <v>8</v>
       </c>
@@ -3434,7 +3437,7 @@
       <c r="G93" s="17"/>
     </row>
     <row r="94" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B94" s="34"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="10">
         <v>9</v>
       </c>
@@ -3450,7 +3453,7 @@
       <c r="G94" s="17"/>
     </row>
     <row r="95" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B95" s="34"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="10">
         <v>10</v>
       </c>
@@ -3466,7 +3469,7 @@
       <c r="G95" s="17"/>
     </row>
     <row r="96" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B96" s="35"/>
+      <c r="B96" s="36"/>
       <c r="C96" s="10">
         <v>11</v>
       </c>
@@ -3482,7 +3485,7 @@
       <c r="G96" s="17"/>
     </row>
     <row r="97" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B97" s="33">
+      <c r="B97" s="34">
         <f>SUM(F97:F103)</f>
         <v>405</v>
       </c>
@@ -3501,7 +3504,7 @@
       <c r="G97" s="17"/>
     </row>
     <row r="98" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B98" s="34"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="10">
         <v>2</v>
       </c>
@@ -3517,7 +3520,7 @@
       <c r="G98" s="17"/>
     </row>
     <row r="99" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B99" s="34"/>
+      <c r="B99" s="35"/>
       <c r="C99" s="10">
         <v>3</v>
       </c>
@@ -3533,7 +3536,7 @@
       <c r="G99" s="17"/>
     </row>
     <row r="100" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B100" s="34"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="10">
         <v>4</v>
       </c>
@@ -3549,7 +3552,7 @@
       <c r="G100" s="17"/>
     </row>
     <row r="101" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B101" s="34"/>
+      <c r="B101" s="35"/>
       <c r="C101" s="10">
         <v>5</v>
       </c>
@@ -3565,7 +3568,7 @@
       <c r="G101" s="17"/>
     </row>
     <row r="102" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B102" s="34"/>
+      <c r="B102" s="35"/>
       <c r="C102" s="10">
         <v>6</v>
       </c>
@@ -3581,7 +3584,7 @@
       <c r="G102" s="17"/>
     </row>
     <row r="103" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B103" s="35"/>
+      <c r="B103" s="36"/>
       <c r="C103" s="10">
         <v>7</v>
       </c>
@@ -3597,7 +3600,7 @@
       <c r="G103" s="17"/>
     </row>
     <row r="104" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B104" s="33">
+      <c r="B104" s="34">
         <f>SUM(F104:F111)</f>
         <v>543</v>
       </c>
@@ -3616,7 +3619,7 @@
       <c r="G104" s="17"/>
     </row>
     <row r="105" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B105" s="34"/>
+      <c r="B105" s="35"/>
       <c r="C105" s="10">
         <v>2</v>
       </c>
@@ -3632,7 +3635,7 @@
       <c r="G105" s="17"/>
     </row>
     <row r="106" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B106" s="34"/>
+      <c r="B106" s="35"/>
       <c r="C106" s="10">
         <v>3</v>
       </c>
@@ -3648,7 +3651,7 @@
       <c r="G106" s="17"/>
     </row>
     <row r="107" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B107" s="34"/>
+      <c r="B107" s="35"/>
       <c r="C107" s="10">
         <v>4</v>
       </c>
@@ -3664,7 +3667,7 @@
       <c r="G107" s="17"/>
     </row>
     <row r="108" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B108" s="34"/>
+      <c r="B108" s="35"/>
       <c r="C108" s="10">
         <v>5</v>
       </c>
@@ -3680,7 +3683,7 @@
       <c r="G108" s="17"/>
     </row>
     <row r="109" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B109" s="34"/>
+      <c r="B109" s="35"/>
       <c r="C109" s="10">
         <v>6</v>
       </c>
@@ -3696,7 +3699,7 @@
       <c r="G109" s="17"/>
     </row>
     <row r="110" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B110" s="34"/>
+      <c r="B110" s="35"/>
       <c r="C110" s="10">
         <v>7</v>
       </c>
@@ -3712,7 +3715,7 @@
       <c r="G110" s="17"/>
     </row>
     <row r="111" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B111" s="35"/>
+      <c r="B111" s="36"/>
       <c r="C111" s="10">
         <v>8</v>
       </c>
@@ -3728,7 +3731,7 @@
       <c r="G111" s="17"/>
     </row>
     <row r="112" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B112" s="33">
+      <c r="B112" s="34">
         <f>SUM(F112:F121)</f>
         <v>403</v>
       </c>
@@ -3747,7 +3750,7 @@
       <c r="G112" s="17"/>
     </row>
     <row r="113" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B113" s="34"/>
+      <c r="B113" s="35"/>
       <c r="C113" s="10">
         <v>2</v>
       </c>
@@ -3763,7 +3766,7 @@
       <c r="G113" s="17"/>
     </row>
     <row r="114" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B114" s="34"/>
+      <c r="B114" s="35"/>
       <c r="C114" s="10">
         <v>3</v>
       </c>
@@ -3779,7 +3782,7 @@
       <c r="G114" s="17"/>
     </row>
     <row r="115" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B115" s="34"/>
+      <c r="B115" s="35"/>
       <c r="C115" s="10">
         <v>4</v>
       </c>
@@ -3795,7 +3798,7 @@
       <c r="G115" s="17"/>
     </row>
     <row r="116" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B116" s="34"/>
+      <c r="B116" s="35"/>
       <c r="C116" s="10">
         <v>5</v>
       </c>
@@ -3811,7 +3814,7 @@
       <c r="G116" s="17"/>
     </row>
     <row r="117" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B117" s="34"/>
+      <c r="B117" s="35"/>
       <c r="C117" s="10">
         <v>6</v>
       </c>
@@ -3827,7 +3830,7 @@
       <c r="G117" s="17"/>
     </row>
     <row r="118" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B118" s="34"/>
+      <c r="B118" s="35"/>
       <c r="C118" s="10">
         <v>7</v>
       </c>
@@ -3841,7 +3844,7 @@
       <c r="G118" s="17"/>
     </row>
     <row r="119" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B119" s="34"/>
+      <c r="B119" s="35"/>
       <c r="C119" s="10">
         <v>8</v>
       </c>
@@ -3857,7 +3860,7 @@
       <c r="G119" s="17"/>
     </row>
     <row r="120" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B120" s="34"/>
+      <c r="B120" s="35"/>
       <c r="C120" s="10">
         <v>9</v>
       </c>
@@ -3873,7 +3876,7 @@
       <c r="G120" s="17"/>
     </row>
     <row r="121" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B121" s="35"/>
+      <c r="B121" s="36"/>
       <c r="C121" s="10">
         <v>10</v>
       </c>
@@ -3889,7 +3892,7 @@
       <c r="G121" s="17"/>
     </row>
     <row r="122" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B122" s="33">
+      <c r="B122" s="34">
         <f>SUM(F122:F129)</f>
         <v>680</v>
       </c>
@@ -3908,7 +3911,7 @@
       <c r="G122" s="17"/>
     </row>
     <row r="123" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B123" s="34"/>
+      <c r="B123" s="35"/>
       <c r="C123" s="10">
         <v>2</v>
       </c>
@@ -3924,7 +3927,7 @@
       <c r="G123" s="17"/>
     </row>
     <row r="124" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B124" s="34"/>
+      <c r="B124" s="35"/>
       <c r="C124" s="10">
         <v>3</v>
       </c>
@@ -3940,7 +3943,7 @@
       <c r="G124" s="17"/>
     </row>
     <row r="125" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B125" s="34"/>
+      <c r="B125" s="35"/>
       <c r="C125" s="10">
         <v>4</v>
       </c>
@@ -3956,7 +3959,7 @@
       <c r="G125" s="17"/>
     </row>
     <row r="126" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B126" s="34"/>
+      <c r="B126" s="35"/>
       <c r="C126" s="10">
         <v>5</v>
       </c>
@@ -3972,7 +3975,7 @@
       <c r="G126" s="17"/>
     </row>
     <row r="127" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B127" s="34"/>
+      <c r="B127" s="35"/>
       <c r="C127" s="10">
         <v>6</v>
       </c>
@@ -3988,7 +3991,7 @@
       <c r="G127" s="17"/>
     </row>
     <row r="128" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B128" s="34"/>
+      <c r="B128" s="35"/>
       <c r="C128" s="10">
         <v>7</v>
       </c>
@@ -4004,7 +4007,7 @@
       <c r="G128" s="17"/>
     </row>
     <row r="129" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B129" s="35"/>
+      <c r="B129" s="36"/>
       <c r="C129" s="10">
         <v>8</v>
       </c>
@@ -4020,7 +4023,7 @@
       <c r="G129" s="17"/>
     </row>
     <row r="130" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B130" s="33">
+      <c r="B130" s="34">
         <f>SUM(F130:F139)</f>
         <v>323</v>
       </c>
@@ -4039,7 +4042,7 @@
       <c r="G130" s="17"/>
     </row>
     <row r="131" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B131" s="34"/>
+      <c r="B131" s="35"/>
       <c r="C131" s="10">
         <v>2</v>
       </c>
@@ -4055,7 +4058,7 @@
       <c r="G131" s="17"/>
     </row>
     <row r="132" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B132" s="34"/>
+      <c r="B132" s="35"/>
       <c r="C132" s="10">
         <v>3</v>
       </c>
@@ -4071,7 +4074,7 @@
       <c r="G132" s="17"/>
     </row>
     <row r="133" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B133" s="34"/>
+      <c r="B133" s="35"/>
       <c r="C133" s="10">
         <v>4</v>
       </c>
@@ -4087,7 +4090,7 @@
       <c r="G133" s="17"/>
     </row>
     <row r="134" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B134" s="34"/>
+      <c r="B134" s="35"/>
       <c r="C134" s="10">
         <v>5</v>
       </c>
@@ -4103,7 +4106,7 @@
       <c r="G134" s="17"/>
     </row>
     <row r="135" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B135" s="34"/>
+      <c r="B135" s="35"/>
       <c r="C135" s="10">
         <v>6</v>
       </c>
@@ -4119,7 +4122,7 @@
       <c r="G135" s="17"/>
     </row>
     <row r="136" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B136" s="34"/>
+      <c r="B136" s="35"/>
       <c r="C136" s="10">
         <v>7</v>
       </c>
@@ -4135,7 +4138,7 @@
       <c r="G136" s="17"/>
     </row>
     <row r="137" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B137" s="34"/>
+      <c r="B137" s="35"/>
       <c r="C137" s="10">
         <v>8</v>
       </c>
@@ -4151,7 +4154,7 @@
       <c r="G137" s="17"/>
     </row>
     <row r="138" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B138" s="34"/>
+      <c r="B138" s="35"/>
       <c r="C138" s="10">
         <v>9</v>
       </c>
@@ -4167,7 +4170,7 @@
       <c r="G138" s="17"/>
     </row>
     <row r="139" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B139" s="35"/>
+      <c r="B139" s="36"/>
       <c r="C139" s="10">
         <v>10</v>
       </c>
@@ -4183,7 +4186,7 @@
       <c r="G139" s="17"/>
     </row>
     <row r="140" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B140" s="33">
+      <c r="B140" s="34">
         <f>SUM(F140:F150)</f>
         <v>380</v>
       </c>
@@ -4202,7 +4205,7 @@
       <c r="G140" s="17"/>
     </row>
     <row r="141" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B141" s="34"/>
+      <c r="B141" s="35"/>
       <c r="C141" s="10">
         <v>2</v>
       </c>
@@ -4218,7 +4221,7 @@
       <c r="G141" s="17"/>
     </row>
     <row r="142" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B142" s="34"/>
+      <c r="B142" s="35"/>
       <c r="C142" s="10">
         <v>3</v>
       </c>
@@ -4234,7 +4237,7 @@
       <c r="G142" s="17"/>
     </row>
     <row r="143" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B143" s="34"/>
+      <c r="B143" s="35"/>
       <c r="C143" s="10">
         <v>4</v>
       </c>
@@ -4250,7 +4253,7 @@
       <c r="G143" s="17"/>
     </row>
     <row r="144" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B144" s="34"/>
+      <c r="B144" s="35"/>
       <c r="C144" s="10">
         <v>5</v>
       </c>
@@ -4266,7 +4269,7 @@
       <c r="G144" s="17"/>
     </row>
     <row r="145" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B145" s="34"/>
+      <c r="B145" s="35"/>
       <c r="C145" s="10">
         <v>6</v>
       </c>
@@ -4282,7 +4285,7 @@
       <c r="G145" s="17"/>
     </row>
     <row r="146" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B146" s="34"/>
+      <c r="B146" s="35"/>
       <c r="C146" s="10">
         <v>7</v>
       </c>
@@ -4298,7 +4301,7 @@
       <c r="G146" s="17"/>
     </row>
     <row r="147" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B147" s="34"/>
+      <c r="B147" s="35"/>
       <c r="C147" s="10">
         <v>8</v>
       </c>
@@ -4314,7 +4317,7 @@
       <c r="G147" s="17"/>
     </row>
     <row r="148" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B148" s="34"/>
+      <c r="B148" s="35"/>
       <c r="C148" s="10">
         <v>9</v>
       </c>
@@ -4330,7 +4333,7 @@
       <c r="G148" s="17"/>
     </row>
     <row r="149" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B149" s="34"/>
+      <c r="B149" s="35"/>
       <c r="C149" s="10">
         <v>10</v>
       </c>
@@ -4346,7 +4349,7 @@
       <c r="G149" s="17"/>
     </row>
     <row r="150" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B150" s="35"/>
+      <c r="B150" s="36"/>
       <c r="C150" s="10">
         <v>11</v>
       </c>
@@ -4362,7 +4365,7 @@
       <c r="G150" s="17"/>
     </row>
     <row r="151" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B151" s="33">
+      <c r="B151" s="34">
         <f>SUM(F151:F158)</f>
         <v>521</v>
       </c>
@@ -4381,7 +4384,7 @@
       <c r="G151" s="17"/>
     </row>
     <row r="152" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B152" s="34"/>
+      <c r="B152" s="35"/>
       <c r="C152" s="10">
         <v>2</v>
       </c>
@@ -4397,7 +4400,7 @@
       <c r="G152" s="17"/>
     </row>
     <row r="153" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B153" s="34"/>
+      <c r="B153" s="35"/>
       <c r="C153" s="10">
         <v>3</v>
       </c>
@@ -4413,7 +4416,7 @@
       <c r="G153" s="17"/>
     </row>
     <row r="154" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B154" s="34"/>
+      <c r="B154" s="35"/>
       <c r="C154" s="10">
         <v>4</v>
       </c>
@@ -4429,7 +4432,7 @@
       <c r="G154" s="17"/>
     </row>
     <row r="155" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B155" s="34"/>
+      <c r="B155" s="35"/>
       <c r="C155" s="10">
         <v>5</v>
       </c>
@@ -4445,7 +4448,7 @@
       <c r="G155" s="17"/>
     </row>
     <row r="156" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B156" s="34"/>
+      <c r="B156" s="35"/>
       <c r="C156" s="10">
         <v>6</v>
       </c>
@@ -4461,7 +4464,7 @@
       <c r="G156" s="17"/>
     </row>
     <row r="157" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B157" s="34"/>
+      <c r="B157" s="35"/>
       <c r="C157" s="10">
         <v>7</v>
       </c>
@@ -4477,7 +4480,7 @@
       <c r="G157" s="17"/>
     </row>
     <row r="158" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B158" s="35"/>
+      <c r="B158" s="36"/>
       <c r="C158" s="10">
         <v>8</v>
       </c>
@@ -4493,7 +4496,7 @@
       <c r="G158" s="17"/>
     </row>
     <row r="159" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B159" s="33">
+      <c r="B159" s="34">
         <f>SUM(F159:F165)</f>
         <v>572</v>
       </c>
@@ -4512,7 +4515,7 @@
       <c r="G159" s="17"/>
     </row>
     <row r="160" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B160" s="34"/>
+      <c r="B160" s="35"/>
       <c r="C160" s="10">
         <v>2</v>
       </c>
@@ -4528,7 +4531,7 @@
       <c r="G160" s="17"/>
     </row>
     <row r="161" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B161" s="34"/>
+      <c r="B161" s="35"/>
       <c r="C161" s="10">
         <v>3</v>
       </c>
@@ -4544,7 +4547,7 @@
       <c r="G161" s="17"/>
     </row>
     <row r="162" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B162" s="34"/>
+      <c r="B162" s="35"/>
       <c r="C162" s="10">
         <v>4</v>
       </c>
@@ -4560,7 +4563,7 @@
       <c r="G162" s="17"/>
     </row>
     <row r="163" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B163" s="34"/>
+      <c r="B163" s="35"/>
       <c r="C163" s="10">
         <v>5</v>
       </c>
@@ -4576,7 +4579,7 @@
       <c r="G163" s="17"/>
     </row>
     <row r="164" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B164" s="34"/>
+      <c r="B164" s="35"/>
       <c r="C164" s="10">
         <v>6</v>
       </c>
@@ -4592,7 +4595,7 @@
       <c r="G164" s="17"/>
     </row>
     <row r="165" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B165" s="35"/>
+      <c r="B165" s="36"/>
       <c r="C165" s="10">
         <v>7</v>
       </c>
@@ -4608,7 +4611,7 @@
       <c r="G165" s="17"/>
     </row>
     <row r="166" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B166" s="33">
+      <c r="B166" s="34">
         <f>SUM(F166:F170)</f>
         <v>270</v>
       </c>
@@ -4627,7 +4630,7 @@
       <c r="G166" s="17"/>
     </row>
     <row r="167" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B167" s="34"/>
+      <c r="B167" s="35"/>
       <c r="C167" s="10">
         <v>2</v>
       </c>
@@ -4643,7 +4646,7 @@
       <c r="G167" s="17"/>
     </row>
     <row r="168" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B168" s="34"/>
+      <c r="B168" s="35"/>
       <c r="C168" s="10">
         <v>3</v>
       </c>
@@ -4659,7 +4662,7 @@
       <c r="G168" s="17"/>
     </row>
     <row r="169" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B169" s="34"/>
+      <c r="B169" s="35"/>
       <c r="C169" s="10">
         <v>4</v>
       </c>
@@ -4675,7 +4678,7 @@
       <c r="G169" s="17"/>
     </row>
     <row r="170" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B170" s="35"/>
+      <c r="B170" s="36"/>
       <c r="C170" s="10">
         <v>5</v>
       </c>
@@ -4691,7 +4694,7 @@
       <c r="G170" s="17"/>
     </row>
     <row r="171" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B171" s="33">
+      <c r="B171" s="34">
         <f>SUM(F171:F176)</f>
         <v>338</v>
       </c>
@@ -4710,7 +4713,7 @@
       <c r="G171" s="17"/>
     </row>
     <row r="172" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B172" s="34"/>
+      <c r="B172" s="35"/>
       <c r="C172" s="10">
         <v>2</v>
       </c>
@@ -4726,7 +4729,7 @@
       <c r="G172" s="17"/>
     </row>
     <row r="173" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B173" s="34"/>
+      <c r="B173" s="35"/>
       <c r="C173" s="10">
         <v>3</v>
       </c>
@@ -4742,7 +4745,7 @@
       <c r="G173" s="17"/>
     </row>
     <row r="174" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B174" s="34"/>
+      <c r="B174" s="35"/>
       <c r="C174" s="10">
         <v>4</v>
       </c>
@@ -4758,7 +4761,7 @@
       <c r="G174" s="17"/>
     </row>
     <row r="175" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B175" s="34"/>
+      <c r="B175" s="35"/>
       <c r="C175" s="10">
         <v>5</v>
       </c>
@@ -4774,7 +4777,7 @@
       <c r="G175" s="17"/>
     </row>
     <row r="176" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B176" s="35"/>
+      <c r="B176" s="36"/>
       <c r="C176" s="10">
         <v>6</v>
       </c>
@@ -4790,7 +4793,7 @@
       <c r="G176" s="17"/>
     </row>
     <row r="177" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B177" s="33">
+      <c r="B177" s="34">
         <f>SUM(F177:F183)</f>
         <v>368</v>
       </c>
@@ -4809,7 +4812,7 @@
       <c r="G177" s="17"/>
     </row>
     <row r="178" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B178" s="34"/>
+      <c r="B178" s="35"/>
       <c r="C178" s="10">
         <v>2</v>
       </c>
@@ -4825,7 +4828,7 @@
       <c r="G178" s="17"/>
     </row>
     <row r="179" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B179" s="34"/>
+      <c r="B179" s="35"/>
       <c r="C179" s="10">
         <v>3</v>
       </c>
@@ -4841,7 +4844,7 @@
       <c r="G179" s="17"/>
     </row>
     <row r="180" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B180" s="34"/>
+      <c r="B180" s="35"/>
       <c r="C180" s="10">
         <v>4</v>
       </c>
@@ -4857,7 +4860,7 @@
       <c r="G180" s="17"/>
     </row>
     <row r="181" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B181" s="34"/>
+      <c r="B181" s="35"/>
       <c r="C181" s="10">
         <v>5</v>
       </c>
@@ -4873,7 +4876,7 @@
       <c r="G181" s="17"/>
     </row>
     <row r="182" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B182" s="34"/>
+      <c r="B182" s="35"/>
       <c r="C182" s="10">
         <v>6</v>
       </c>
@@ -4889,7 +4892,7 @@
       <c r="G182" s="17"/>
     </row>
     <row r="183" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B183" s="35"/>
+      <c r="B183" s="36"/>
       <c r="C183" s="10">
         <v>7</v>
       </c>
@@ -4905,7 +4908,7 @@
       <c r="G183" s="17"/>
     </row>
     <row r="184" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B184" s="33">
+      <c r="B184" s="34">
         <f>SUM(F184:F193)</f>
         <v>345</v>
       </c>
@@ -4924,7 +4927,7 @@
       <c r="G184" s="17"/>
     </row>
     <row r="185" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B185" s="34"/>
+      <c r="B185" s="35"/>
       <c r="C185" s="10">
         <v>2</v>
       </c>
@@ -4940,7 +4943,7 @@
       <c r="G185" s="17"/>
     </row>
     <row r="186" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B186" s="34"/>
+      <c r="B186" s="35"/>
       <c r="C186" s="10">
         <v>3</v>
       </c>
@@ -4956,7 +4959,7 @@
       <c r="G186" s="17"/>
     </row>
     <row r="187" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B187" s="34"/>
+      <c r="B187" s="35"/>
       <c r="C187" s="10">
         <v>4</v>
       </c>
@@ -4972,7 +4975,7 @@
       <c r="G187" s="17"/>
     </row>
     <row r="188" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B188" s="34"/>
+      <c r="B188" s="35"/>
       <c r="C188" s="10">
         <v>5</v>
       </c>
@@ -4988,7 +4991,7 @@
       <c r="G188" s="17"/>
     </row>
     <row r="189" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B189" s="34"/>
+      <c r="B189" s="35"/>
       <c r="C189" s="10">
         <v>6</v>
       </c>
@@ -5004,7 +5007,7 @@
       <c r="G189" s="17"/>
     </row>
     <row r="190" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B190" s="34"/>
+      <c r="B190" s="35"/>
       <c r="C190" s="10">
         <v>7</v>
       </c>
@@ -5020,7 +5023,7 @@
       <c r="G190" s="17"/>
     </row>
     <row r="191" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B191" s="34"/>
+      <c r="B191" s="35"/>
       <c r="C191" s="10">
         <v>8</v>
       </c>
@@ -5036,7 +5039,7 @@
       <c r="G191" s="17"/>
     </row>
     <row r="192" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B192" s="34"/>
+      <c r="B192" s="35"/>
       <c r="C192" s="10">
         <v>9</v>
       </c>
@@ -5052,7 +5055,7 @@
       <c r="G192" s="17"/>
     </row>
     <row r="193" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B193" s="35"/>
+      <c r="B193" s="36"/>
       <c r="C193" s="10">
         <v>10</v>
       </c>
@@ -5068,7 +5071,7 @@
       <c r="G193" s="17"/>
     </row>
     <row r="194" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B194" s="33">
+      <c r="B194" s="34">
         <f>SUM(F194:F201)</f>
         <v>253</v>
       </c>
@@ -5087,7 +5090,7 @@
       <c r="G194" s="17"/>
     </row>
     <row r="195" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B195" s="34"/>
+      <c r="B195" s="35"/>
       <c r="C195" s="10">
         <v>2</v>
       </c>
@@ -5103,7 +5106,7 @@
       <c r="G195" s="17"/>
     </row>
     <row r="196" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B196" s="34"/>
+      <c r="B196" s="35"/>
       <c r="C196" s="10">
         <v>3</v>
       </c>
@@ -5119,7 +5122,7 @@
       <c r="G196" s="17"/>
     </row>
     <row r="197" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B197" s="34"/>
+      <c r="B197" s="35"/>
       <c r="C197" s="10">
         <v>4</v>
       </c>
@@ -5136,7 +5139,7 @@
       <c r="I197" s="20"/>
     </row>
     <row r="198" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B198" s="34"/>
+      <c r="B198" s="35"/>
       <c r="C198" s="10">
         <v>5</v>
       </c>
@@ -5154,7 +5157,7 @@
       <c r="I198" s="20"/>
     </row>
     <row r="199" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B199" s="34"/>
+      <c r="B199" s="35"/>
       <c r="C199" s="10">
         <v>6</v>
       </c>
@@ -5172,7 +5175,7 @@
       <c r="I199" s="20"/>
     </row>
     <row r="200" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B200" s="34"/>
+      <c r="B200" s="35"/>
       <c r="C200" s="10">
         <v>7</v>
       </c>
@@ -5190,7 +5193,7 @@
       <c r="I200" s="20"/>
     </row>
     <row r="201" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B201" s="35"/>
+      <c r="B201" s="36"/>
       <c r="C201" s="10">
         <v>8</v>
       </c>
@@ -5208,7 +5211,7 @@
       <c r="I201" s="20"/>
     </row>
     <row r="202" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B202" s="33">
+      <c r="B202" s="34">
         <f>SUM(F202:F206)</f>
         <v>180</v>
       </c>
@@ -5229,7 +5232,7 @@
       <c r="I202" s="20"/>
     </row>
     <row r="203" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B203" s="34"/>
+      <c r="B203" s="35"/>
       <c r="C203" s="10">
         <v>2</v>
       </c>
@@ -5247,7 +5250,7 @@
       <c r="I203" s="20"/>
     </row>
     <row r="204" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B204" s="34"/>
+      <c r="B204" s="35"/>
       <c r="C204" s="10">
         <v>3</v>
       </c>
@@ -5265,7 +5268,7 @@
       <c r="I204" s="20"/>
     </row>
     <row r="205" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B205" s="34"/>
+      <c r="B205" s="35"/>
       <c r="C205" s="10">
         <v>4</v>
       </c>
@@ -5283,7 +5286,7 @@
       <c r="I205" s="20"/>
     </row>
     <row r="206" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B206" s="35"/>
+      <c r="B206" s="36"/>
       <c r="C206" s="10">
         <v>5</v>
       </c>
@@ -5301,7 +5304,7 @@
       <c r="I206" s="20"/>
     </row>
     <row r="207" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B207" s="33">
+      <c r="B207" s="34">
         <f>SUM(F207:F210)</f>
         <v>1027</v>
       </c>
@@ -5318,7 +5321,7 @@
       <c r="I207" s="20"/>
     </row>
     <row r="208" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B208" s="34"/>
+      <c r="B208" s="35"/>
       <c r="C208" s="10">
         <v>2</v>
       </c>
@@ -5336,7 +5339,7 @@
       <c r="I208" s="20"/>
     </row>
     <row r="209" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B209" s="34"/>
+      <c r="B209" s="35"/>
       <c r="C209" s="10">
         <v>3</v>
       </c>
@@ -5354,7 +5357,7 @@
       <c r="I209" s="20"/>
     </row>
     <row r="210" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B210" s="35"/>
+      <c r="B210" s="36"/>
       <c r="C210" s="10">
         <v>4</v>
       </c>
@@ -5397,6 +5400,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B184:B193"/>
+    <mergeCell ref="B194:B201"/>
+    <mergeCell ref="B202:B206"/>
+    <mergeCell ref="B177:B183"/>
+    <mergeCell ref="B166:B170"/>
+    <mergeCell ref="B171:B176"/>
+    <mergeCell ref="B86:B96"/>
+    <mergeCell ref="B122:B129"/>
+    <mergeCell ref="B112:B121"/>
+    <mergeCell ref="B104:B111"/>
+    <mergeCell ref="B151:B158"/>
+    <mergeCell ref="B140:B150"/>
     <mergeCell ref="B207:B210"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="D1:F2"/>
@@ -5413,18 +5428,6 @@
     <mergeCell ref="B97:B103"/>
     <mergeCell ref="B130:B139"/>
     <mergeCell ref="B159:B165"/>
-    <mergeCell ref="B86:B96"/>
-    <mergeCell ref="B122:B129"/>
-    <mergeCell ref="B112:B121"/>
-    <mergeCell ref="B104:B111"/>
-    <mergeCell ref="B151:B158"/>
-    <mergeCell ref="B140:B150"/>
-    <mergeCell ref="B184:B193"/>
-    <mergeCell ref="B194:B201"/>
-    <mergeCell ref="B202:B206"/>
-    <mergeCell ref="B177:B183"/>
-    <mergeCell ref="B166:B170"/>
-    <mergeCell ref="B171:B176"/>
   </mergeCells>
   <conditionalFormatting sqref="F1:F1048576">
     <cfRule type="cellIs" dxfId="73" priority="1" operator="between">
@@ -5475,20 +5478,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="22.5" customHeight="1">
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="36">
+      <c r="E1" s="39"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="37">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="36"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
       <c r="C3" s="7" t="s">
@@ -5508,7 +5511,7 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>SUM(F4:F18)</f>
         <v>582</v>
       </c>
@@ -5536,7 +5539,7 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="5">
         <v>2</v>
       </c>
@@ -5558,7 +5561,7 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="5">
         <v>3</v>
       </c>
@@ -5580,7 +5583,7 @@
       </c>
     </row>
     <row r="7" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="5">
         <v>4</v>
       </c>
@@ -5602,7 +5605,7 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="5">
         <v>5</v>
       </c>
@@ -5624,7 +5627,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="5">
         <v>6</v>
       </c>
@@ -5646,7 +5649,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="5">
         <v>7</v>
       </c>
@@ -5668,7 +5671,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="5">
         <v>8</v>
       </c>
@@ -5690,7 +5693,7 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="5">
         <v>9</v>
       </c>
@@ -5712,7 +5715,7 @@
       </c>
     </row>
     <row r="13" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B13" s="34"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="5">
         <v>10</v>
       </c>
@@ -5734,7 +5737,7 @@
       </c>
     </row>
     <row r="14" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B14" s="34"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="5">
         <v>11</v>
       </c>
@@ -5756,7 +5759,7 @@
       </c>
     </row>
     <row r="15" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B15" s="34"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="5">
         <v>12</v>
       </c>
@@ -5778,7 +5781,7 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B16" s="34"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="5">
         <v>13</v>
       </c>
@@ -5800,7 +5803,7 @@
       </c>
     </row>
     <row r="17" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B17" s="34"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="5">
         <v>14</v>
       </c>
@@ -5822,7 +5825,7 @@
       </c>
     </row>
     <row r="18" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B18" s="35"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="5">
         <v>15</v>
       </c>
@@ -5844,7 +5847,7 @@
       </c>
     </row>
     <row r="19" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B19" s="33">
+      <c r="B19" s="34">
         <f>SUM(F19:F26)</f>
         <v>342</v>
       </c>
@@ -5869,7 +5872,7 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B20" s="34"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="5">
         <v>2</v>
       </c>
@@ -5891,7 +5894,7 @@
       </c>
     </row>
     <row r="21" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B21" s="34"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="5">
         <v>3</v>
       </c>
@@ -5913,7 +5916,7 @@
       </c>
     </row>
     <row r="22" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B22" s="34"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="5">
         <v>4</v>
       </c>
@@ -5935,7 +5938,7 @@
       </c>
     </row>
     <row r="23" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B23" s="34"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="5">
         <v>5</v>
       </c>
@@ -5957,7 +5960,7 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B24" s="34"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="5">
         <v>6</v>
       </c>
@@ -5979,7 +5982,7 @@
       </c>
     </row>
     <row r="25" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="5">
         <v>7</v>
       </c>
@@ -6001,7 +6004,7 @@
       </c>
     </row>
     <row r="26" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B26" s="34"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="5">
         <v>8</v>
       </c>
@@ -6023,7 +6026,7 @@
       </c>
     </row>
     <row r="27" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B27" s="33">
+      <c r="B27" s="34">
         <f>SUM(F27:F38)</f>
         <v>399</v>
       </c>
@@ -6048,7 +6051,7 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B28" s="34"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="5">
         <v>2</v>
       </c>
@@ -6070,7 +6073,7 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="5">
         <v>3</v>
       </c>
@@ -6092,7 +6095,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B30" s="34"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="5">
         <v>4</v>
       </c>
@@ -6114,7 +6117,7 @@
       </c>
     </row>
     <row r="31" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="5">
         <v>5</v>
       </c>
@@ -6136,7 +6139,7 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="5">
         <v>6</v>
       </c>
@@ -6158,7 +6161,7 @@
       </c>
     </row>
     <row r="33" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="5">
         <v>7</v>
       </c>
@@ -6180,7 +6183,7 @@
       </c>
     </row>
     <row r="34" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="5">
         <v>8</v>
       </c>
@@ -6196,7 +6199,7 @@
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="5">
         <v>9</v>
       </c>
@@ -6212,7 +6215,7 @@
       <c r="G35" s="6"/>
     </row>
     <row r="36" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="5">
         <v>10</v>
       </c>
@@ -6228,7 +6231,7 @@
       <c r="G36" s="6"/>
     </row>
     <row r="37" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B37" s="34"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="5">
         <v>11</v>
       </c>
@@ -6244,7 +6247,7 @@
       <c r="G37" s="6"/>
     </row>
     <row r="38" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B38" s="35"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="5">
         <v>12</v>
       </c>
@@ -6260,7 +6263,7 @@
       <c r="G38" s="6"/>
     </row>
     <row r="39" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B39" s="33">
+      <c r="B39" s="34">
         <f>SUM(F39:F45)</f>
         <v>235</v>
       </c>
@@ -6279,7 +6282,7 @@
       <c r="G39" s="6"/>
     </row>
     <row r="40" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B40" s="34"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="5">
         <v>2</v>
       </c>
@@ -6295,7 +6298,7 @@
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B41" s="34"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="5">
         <v>3</v>
       </c>
@@ -6311,7 +6314,7 @@
       <c r="G41" s="6"/>
     </row>
     <row r="42" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B42" s="34"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="5">
         <v>4</v>
       </c>
@@ -6327,7 +6330,7 @@
       <c r="G42" s="6"/>
     </row>
     <row r="43" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B43" s="34"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="5">
         <v>5</v>
       </c>
@@ -6343,7 +6346,7 @@
       <c r="G43" s="6"/>
     </row>
     <row r="44" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B44" s="34"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="5">
         <v>6</v>
       </c>
@@ -6359,7 +6362,7 @@
       <c r="G44" s="6"/>
     </row>
     <row r="45" spans="2:9" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B45" s="35"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="5">
         <v>7</v>
       </c>
@@ -6375,7 +6378,7 @@
       <c r="G45" s="6"/>
     </row>
     <row r="46" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B46" s="33">
+      <c r="B46" s="34">
         <f>SUM(F46:F53)</f>
         <v>245</v>
       </c>
@@ -6394,7 +6397,7 @@
       <c r="G46" s="6"/>
     </row>
     <row r="47" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B47" s="34"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="5">
         <v>2</v>
       </c>
@@ -6410,7 +6413,7 @@
       <c r="G47" s="17"/>
     </row>
     <row r="48" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B48" s="34"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="5">
         <v>3</v>
       </c>
@@ -6426,7 +6429,7 @@
       <c r="G48" s="17"/>
     </row>
     <row r="49" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B49" s="34"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="5">
         <v>4</v>
       </c>
@@ -6442,7 +6445,7 @@
       <c r="G49" s="17"/>
     </row>
     <row r="50" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B50" s="34"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="5">
         <v>5</v>
       </c>
@@ -6458,7 +6461,7 @@
       <c r="G50" s="17"/>
     </row>
     <row r="51" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B51" s="34"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="5">
         <v>6</v>
       </c>
@@ -6472,7 +6475,7 @@
       <c r="G51" s="17"/>
     </row>
     <row r="52" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B52" s="34"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="5">
         <v>7</v>
       </c>
@@ -6488,7 +6491,7 @@
       <c r="G52" s="17"/>
     </row>
     <row r="53" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B53" s="35"/>
+      <c r="B53" s="36"/>
       <c r="C53" s="5">
         <v>8</v>
       </c>
@@ -6504,7 +6507,7 @@
       <c r="G53" s="17"/>
     </row>
     <row r="54" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B54" s="33">
+      <c r="B54" s="34">
         <f>SUM(F54:F67)</f>
         <v>556</v>
       </c>
@@ -6523,7 +6526,7 @@
       <c r="G54" s="17"/>
     </row>
     <row r="55" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B55" s="34"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="10">
         <v>2</v>
       </c>
@@ -6539,7 +6542,7 @@
       <c r="G55" s="17"/>
     </row>
     <row r="56" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B56" s="34"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="10">
         <v>3</v>
       </c>
@@ -6555,7 +6558,7 @@
       <c r="G56" s="17"/>
     </row>
     <row r="57" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B57" s="34"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="10">
         <v>4</v>
       </c>
@@ -6571,7 +6574,7 @@
       <c r="G57" s="17"/>
     </row>
     <row r="58" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B58" s="34"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="10">
         <v>5</v>
       </c>
@@ -6587,7 +6590,7 @@
       <c r="G58" s="17"/>
     </row>
     <row r="59" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B59" s="34"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="10">
         <v>6</v>
       </c>
@@ -6603,7 +6606,7 @@
       <c r="G59" s="17"/>
     </row>
     <row r="60" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B60" s="34"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="10">
         <v>7</v>
       </c>
@@ -6619,7 +6622,7 @@
       <c r="G60" s="17"/>
     </row>
     <row r="61" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B61" s="34"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="10">
         <v>8</v>
       </c>
@@ -6635,7 +6638,7 @@
       <c r="G61" s="17"/>
     </row>
     <row r="62" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B62" s="34"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="10">
         <v>9</v>
       </c>
@@ -6651,7 +6654,7 @@
       <c r="G62" s="17"/>
     </row>
     <row r="63" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B63" s="34"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="10">
         <v>10</v>
       </c>
@@ -6667,7 +6670,7 @@
       <c r="G63" s="17"/>
     </row>
     <row r="64" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B64" s="34"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="10">
         <v>11</v>
       </c>
@@ -6683,7 +6686,7 @@
       <c r="G64" s="17"/>
     </row>
     <row r="65" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B65" s="34"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="10">
         <v>12</v>
       </c>
@@ -6699,7 +6702,7 @@
       <c r="G65" s="17"/>
     </row>
     <row r="66" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B66" s="34"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="10">
         <v>13</v>
       </c>
@@ -6715,7 +6718,7 @@
       <c r="G66" s="17"/>
     </row>
     <row r="67" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B67" s="35"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="10">
         <v>14</v>
       </c>
@@ -6731,7 +6734,7 @@
       <c r="G67" s="17"/>
     </row>
     <row r="68" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B68" s="33">
+      <c r="B68" s="34">
         <f>SUM(F68:F75)</f>
         <v>345</v>
       </c>
@@ -6750,7 +6753,7 @@
       <c r="G68" s="17"/>
     </row>
     <row r="69" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B69" s="34"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="10">
         <v>2</v>
       </c>
@@ -6766,7 +6769,7 @@
       <c r="G69" s="17"/>
     </row>
     <row r="70" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B70" s="34"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="10">
         <v>3</v>
       </c>
@@ -6782,7 +6785,7 @@
       <c r="G70" s="17"/>
     </row>
     <row r="71" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B71" s="34"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="10">
         <v>4</v>
       </c>
@@ -6798,7 +6801,7 @@
       <c r="G71" s="17"/>
     </row>
     <row r="72" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B72" s="34"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="10">
         <v>5</v>
       </c>
@@ -6814,7 +6817,7 @@
       <c r="G72" s="17"/>
     </row>
     <row r="73" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B73" s="34"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="10">
         <v>6</v>
       </c>
@@ -6830,7 +6833,7 @@
       <c r="G73" s="17"/>
     </row>
     <row r="74" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B74" s="34"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="10">
         <v>7</v>
       </c>
@@ -6846,7 +6849,7 @@
       <c r="G74" s="17"/>
     </row>
     <row r="75" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B75" s="35"/>
+      <c r="B75" s="36"/>
       <c r="C75" s="10">
         <v>8</v>
       </c>
@@ -6862,7 +6865,7 @@
       <c r="G75" s="17"/>
     </row>
     <row r="76" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B76" s="33">
+      <c r="B76" s="34">
         <f>SUM(F76:F85)</f>
         <v>624</v>
       </c>
@@ -6881,7 +6884,7 @@
       <c r="G76" s="17"/>
     </row>
     <row r="77" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B77" s="34"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="10">
         <v>2</v>
       </c>
@@ -6897,7 +6900,7 @@
       <c r="G77" s="17"/>
     </row>
     <row r="78" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B78" s="34"/>
+      <c r="B78" s="35"/>
       <c r="C78" s="10">
         <v>3</v>
       </c>
@@ -6913,7 +6916,7 @@
       <c r="G78" s="17"/>
     </row>
     <row r="79" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B79" s="34"/>
+      <c r="B79" s="35"/>
       <c r="C79" s="10">
         <v>4</v>
       </c>
@@ -6929,7 +6932,7 @@
       <c r="G79" s="17"/>
     </row>
     <row r="80" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B80" s="34"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="10">
         <v>5</v>
       </c>
@@ -6945,7 +6948,7 @@
       <c r="G80" s="17"/>
     </row>
     <row r="81" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B81" s="34"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="10">
         <v>6</v>
       </c>
@@ -6961,7 +6964,7 @@
       <c r="G81" s="17"/>
     </row>
     <row r="82" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B82" s="34"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="10">
         <v>7</v>
       </c>
@@ -6977,7 +6980,7 @@
       <c r="G82" s="17"/>
     </row>
     <row r="83" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="10">
         <v>8</v>
       </c>
@@ -6993,7 +6996,7 @@
       <c r="G83" s="17"/>
     </row>
     <row r="84" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="10">
         <v>9</v>
       </c>
@@ -7009,7 +7012,7 @@
       <c r="G84" s="17"/>
     </row>
     <row r="85" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B85" s="34"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="10">
         <v>10</v>
       </c>
@@ -7025,7 +7028,7 @@
       <c r="G85" s="17"/>
     </row>
     <row r="86" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B86" s="33">
+      <c r="B86" s="34">
         <f>SUM(F86:F95)</f>
         <v>422</v>
       </c>
@@ -7044,7 +7047,7 @@
       <c r="G86" s="17"/>
     </row>
     <row r="87" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B87" s="34"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="10">
         <v>2</v>
       </c>
@@ -7060,7 +7063,7 @@
       <c r="G87" s="17"/>
     </row>
     <row r="88" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B88" s="34"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="10">
         <v>3</v>
       </c>
@@ -7076,7 +7079,7 @@
       <c r="G88" s="17"/>
     </row>
     <row r="89" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B89" s="34"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="10">
         <v>4</v>
       </c>
@@ -7092,7 +7095,7 @@
       <c r="G89" s="17"/>
     </row>
     <row r="90" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B90" s="34"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="10">
         <v>5</v>
       </c>
@@ -7108,7 +7111,7 @@
       <c r="G90" s="17"/>
     </row>
     <row r="91" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B91" s="34"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="10">
         <v>6</v>
       </c>
@@ -7124,7 +7127,7 @@
       <c r="G91" s="17"/>
     </row>
     <row r="92" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B92" s="34"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="10">
         <v>7</v>
       </c>
@@ -7140,7 +7143,7 @@
       <c r="G92" s="17"/>
     </row>
     <row r="93" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B93" s="34"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="10">
         <v>8</v>
       </c>
@@ -7156,7 +7159,7 @@
       <c r="G93" s="17"/>
     </row>
     <row r="94" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B94" s="34"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="10">
         <v>9</v>
       </c>
@@ -7172,7 +7175,7 @@
       <c r="G94" s="17"/>
     </row>
     <row r="95" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B95" s="35"/>
+      <c r="B95" s="36"/>
       <c r="C95" s="10">
         <v>10</v>
       </c>
@@ -7188,7 +7191,7 @@
       <c r="G95" s="17"/>
     </row>
     <row r="96" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B96" s="33">
+      <c r="B96" s="34">
         <f>SUM(F96:F102)</f>
         <v>222</v>
       </c>
@@ -7207,7 +7210,7 @@
       <c r="G96" s="17"/>
     </row>
     <row r="97" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B97" s="34"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="10">
         <v>2</v>
       </c>
@@ -7223,7 +7226,7 @@
       <c r="G97" s="17"/>
     </row>
     <row r="98" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B98" s="34"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="10">
         <v>3</v>
       </c>
@@ -7239,7 +7242,7 @@
       <c r="G98" s="17"/>
     </row>
     <row r="99" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B99" s="34"/>
+      <c r="B99" s="35"/>
       <c r="C99" s="10">
         <v>4</v>
       </c>
@@ -7255,7 +7258,7 @@
       <c r="G99" s="17"/>
     </row>
     <row r="100" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B100" s="34"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="10">
         <v>5</v>
       </c>
@@ -7271,7 +7274,7 @@
       <c r="G100" s="17"/>
     </row>
     <row r="101" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B101" s="34"/>
+      <c r="B101" s="35"/>
       <c r="C101" s="10">
         <v>6</v>
       </c>
@@ -7287,7 +7290,7 @@
       <c r="G101" s="17"/>
     </row>
     <row r="102" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B102" s="35"/>
+      <c r="B102" s="36"/>
       <c r="C102" s="10">
         <v>7</v>
       </c>
@@ -7303,7 +7306,7 @@
       <c r="G102" s="17"/>
     </row>
     <row r="103" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B103" s="33">
+      <c r="B103" s="34">
         <f>SUM(F103:F111)</f>
         <v>380</v>
       </c>
@@ -7322,7 +7325,7 @@
       <c r="G103" s="17"/>
     </row>
     <row r="104" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B104" s="34"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="10">
         <v>2</v>
       </c>
@@ -7338,7 +7341,7 @@
       <c r="G104" s="17"/>
     </row>
     <row r="105" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B105" s="34"/>
+      <c r="B105" s="35"/>
       <c r="C105" s="10">
         <v>3</v>
       </c>
@@ -7354,7 +7357,7 @@
       <c r="G105" s="17"/>
     </row>
     <row r="106" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B106" s="34"/>
+      <c r="B106" s="35"/>
       <c r="C106" s="10">
         <v>4</v>
       </c>
@@ -7370,7 +7373,7 @@
       <c r="G106" s="17"/>
     </row>
     <row r="107" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B107" s="34"/>
+      <c r="B107" s="35"/>
       <c r="C107" s="10">
         <v>5</v>
       </c>
@@ -7386,7 +7389,7 @@
       <c r="G107" s="17"/>
     </row>
     <row r="108" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B108" s="34"/>
+      <c r="B108" s="35"/>
       <c r="C108" s="10">
         <v>6</v>
       </c>
@@ -7402,7 +7405,7 @@
       <c r="G108" s="17"/>
     </row>
     <row r="109" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B109" s="34"/>
+      <c r="B109" s="35"/>
       <c r="C109" s="10">
         <v>7</v>
       </c>
@@ -7418,7 +7421,7 @@
       <c r="G109" s="17"/>
     </row>
     <row r="110" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B110" s="34"/>
+      <c r="B110" s="35"/>
       <c r="C110" s="10">
         <v>8</v>
       </c>
@@ -7434,7 +7437,7 @@
       <c r="G110" s="17"/>
     </row>
     <row r="111" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B111" s="34"/>
+      <c r="B111" s="35"/>
       <c r="C111" s="10">
         <v>9</v>
       </c>
@@ -7450,7 +7453,7 @@
       <c r="G111" s="17"/>
     </row>
     <row r="112" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B112" s="33">
+      <c r="B112" s="34">
         <f>SUM(F112:F118)</f>
         <v>275</v>
       </c>
@@ -7469,7 +7472,7 @@
       <c r="G112" s="17"/>
     </row>
     <row r="113" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B113" s="34"/>
+      <c r="B113" s="35"/>
       <c r="C113" s="10">
         <v>2</v>
       </c>
@@ -7485,7 +7488,7 @@
       <c r="G113" s="17"/>
     </row>
     <row r="114" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B114" s="34"/>
+      <c r="B114" s="35"/>
       <c r="C114" s="10">
         <v>3</v>
       </c>
@@ -7501,7 +7504,7 @@
       <c r="G114" s="17"/>
     </row>
     <row r="115" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B115" s="34"/>
+      <c r="B115" s="35"/>
       <c r="C115" s="10">
         <v>4</v>
       </c>
@@ -7517,7 +7520,7 @@
       <c r="G115" s="17"/>
     </row>
     <row r="116" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B116" s="34"/>
+      <c r="B116" s="35"/>
       <c r="C116" s="10">
         <v>5</v>
       </c>
@@ -7533,7 +7536,7 @@
       <c r="G116" s="17"/>
     </row>
     <row r="117" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B117" s="34"/>
+      <c r="B117" s="35"/>
       <c r="C117" s="10">
         <v>6</v>
       </c>
@@ -7549,7 +7552,7 @@
       <c r="G117" s="17"/>
     </row>
     <row r="118" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B118" s="35"/>
+      <c r="B118" s="36"/>
       <c r="C118" s="10">
         <v>7</v>
       </c>
@@ -7565,7 +7568,7 @@
       <c r="G118" s="17"/>
     </row>
     <row r="119" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B119" s="33">
+      <c r="B119" s="34">
         <f>SUM(F119:F124)</f>
         <v>285</v>
       </c>
@@ -7584,7 +7587,7 @@
       <c r="G119" s="17"/>
     </row>
     <row r="120" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B120" s="34"/>
+      <c r="B120" s="35"/>
       <c r="C120" s="10">
         <v>2</v>
       </c>
@@ -7600,7 +7603,7 @@
       <c r="G120" s="17"/>
     </row>
     <row r="121" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B121" s="34"/>
+      <c r="B121" s="35"/>
       <c r="C121" s="10">
         <v>3</v>
       </c>
@@ -7616,7 +7619,7 @@
       <c r="G121" s="17"/>
     </row>
     <row r="122" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B122" s="34"/>
+      <c r="B122" s="35"/>
       <c r="C122" s="10">
         <v>4</v>
       </c>
@@ -7632,7 +7635,7 @@
       <c r="G122" s="17"/>
     </row>
     <row r="123" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B123" s="34"/>
+      <c r="B123" s="35"/>
       <c r="C123" s="10">
         <v>5</v>
       </c>
@@ -7648,7 +7651,7 @@
       <c r="G123" s="17"/>
     </row>
     <row r="124" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B124" s="34"/>
+      <c r="B124" s="35"/>
       <c r="C124" s="10">
         <v>6</v>
       </c>
@@ -7664,7 +7667,7 @@
       <c r="G124" s="17"/>
     </row>
     <row r="125" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B125" s="33">
+      <c r="B125" s="34">
         <f>SUM(F125:F128)</f>
         <v>275</v>
       </c>
@@ -7683,7 +7686,7 @@
       <c r="G125" s="17"/>
     </row>
     <row r="126" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B126" s="34"/>
+      <c r="B126" s="35"/>
       <c r="C126" s="10">
         <v>2</v>
       </c>
@@ -7699,7 +7702,7 @@
       <c r="G126" s="17"/>
     </row>
     <row r="127" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B127" s="34"/>
+      <c r="B127" s="35"/>
       <c r="C127" s="10">
         <v>3</v>
       </c>
@@ -7715,7 +7718,7 @@
       <c r="G127" s="17"/>
     </row>
     <row r="128" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B128" s="34"/>
+      <c r="B128" s="35"/>
       <c r="C128" s="10">
         <v>4</v>
       </c>
@@ -7731,7 +7734,7 @@
       <c r="G128" s="17"/>
     </row>
     <row r="129" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B129" s="33">
+      <c r="B129" s="34">
         <f>SUM(F129:F140)</f>
         <v>372</v>
       </c>
@@ -7750,7 +7753,7 @@
       <c r="G129" s="17"/>
     </row>
     <row r="130" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B130" s="34"/>
+      <c r="B130" s="35"/>
       <c r="C130" s="10">
         <v>2</v>
       </c>
@@ -7766,7 +7769,7 @@
       <c r="G130" s="17"/>
     </row>
     <row r="131" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B131" s="34"/>
+      <c r="B131" s="35"/>
       <c r="C131" s="10">
         <v>3</v>
       </c>
@@ -7782,7 +7785,7 @@
       <c r="G131" s="17"/>
     </row>
     <row r="132" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B132" s="34"/>
+      <c r="B132" s="35"/>
       <c r="C132" s="10">
         <v>4</v>
       </c>
@@ -7798,7 +7801,7 @@
       <c r="G132" s="17"/>
     </row>
     <row r="133" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B133" s="34"/>
+      <c r="B133" s="35"/>
       <c r="C133" s="10">
         <v>5</v>
       </c>
@@ -7814,7 +7817,7 @@
       <c r="G133" s="17"/>
     </row>
     <row r="134" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B134" s="34"/>
+      <c r="B134" s="35"/>
       <c r="C134" s="10">
         <v>6</v>
       </c>
@@ -7830,7 +7833,7 @@
       <c r="G134" s="17"/>
     </row>
     <row r="135" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B135" s="34"/>
+      <c r="B135" s="35"/>
       <c r="C135" s="10">
         <v>7</v>
       </c>
@@ -7846,7 +7849,7 @@
       <c r="G135" s="17"/>
     </row>
     <row r="136" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B136" s="34"/>
+      <c r="B136" s="35"/>
       <c r="C136" s="10">
         <v>8</v>
       </c>
@@ -7862,7 +7865,7 @@
       <c r="G136" s="17"/>
     </row>
     <row r="137" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B137" s="34"/>
+      <c r="B137" s="35"/>
       <c r="C137" s="10">
         <v>9</v>
       </c>
@@ -7878,7 +7881,7 @@
       <c r="G137" s="17"/>
     </row>
     <row r="138" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B138" s="34"/>
+      <c r="B138" s="35"/>
       <c r="C138" s="10">
         <v>10</v>
       </c>
@@ -7894,7 +7897,7 @@
       <c r="G138" s="17"/>
     </row>
     <row r="139" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B139" s="34"/>
+      <c r="B139" s="35"/>
       <c r="C139" s="10">
         <v>11</v>
       </c>
@@ -7910,7 +7913,7 @@
       <c r="G139" s="17"/>
     </row>
     <row r="140" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B140" s="35"/>
+      <c r="B140" s="36"/>
       <c r="C140" s="10">
         <v>12</v>
       </c>
@@ -7926,7 +7929,7 @@
       <c r="G140" s="17"/>
     </row>
     <row r="141" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B141" s="33">
+      <c r="B141" s="34">
         <f>SUM(F141:F151)</f>
         <v>307</v>
       </c>
@@ -7945,7 +7948,7 @@
       <c r="G141" s="17"/>
     </row>
     <row r="142" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B142" s="34"/>
+      <c r="B142" s="35"/>
       <c r="C142" s="10">
         <v>2</v>
       </c>
@@ -7961,7 +7964,7 @@
       <c r="G142" s="17"/>
     </row>
     <row r="143" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B143" s="34"/>
+      <c r="B143" s="35"/>
       <c r="C143" s="10">
         <v>3</v>
       </c>
@@ -7977,7 +7980,7 @@
       <c r="G143" s="17"/>
     </row>
     <row r="144" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B144" s="34"/>
+      <c r="B144" s="35"/>
       <c r="C144" s="10">
         <v>4</v>
       </c>
@@ -7993,7 +7996,7 @@
       <c r="G144" s="17"/>
     </row>
     <row r="145" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B145" s="34"/>
+      <c r="B145" s="35"/>
       <c r="C145" s="10">
         <v>5</v>
       </c>
@@ -8009,7 +8012,7 @@
       <c r="G145" s="17"/>
     </row>
     <row r="146" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B146" s="34"/>
+      <c r="B146" s="35"/>
       <c r="C146" s="10">
         <v>6</v>
       </c>
@@ -8025,7 +8028,7 @@
       <c r="G146" s="17"/>
     </row>
     <row r="147" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B147" s="34"/>
+      <c r="B147" s="35"/>
       <c r="C147" s="10">
         <v>7</v>
       </c>
@@ -8041,7 +8044,7 @@
       <c r="G147" s="17"/>
     </row>
     <row r="148" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B148" s="34"/>
+      <c r="B148" s="35"/>
       <c r="C148" s="10">
         <v>8</v>
       </c>
@@ -8057,7 +8060,7 @@
       <c r="G148" s="17"/>
     </row>
     <row r="149" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B149" s="34"/>
+      <c r="B149" s="35"/>
       <c r="C149" s="10">
         <v>9</v>
       </c>
@@ -8073,7 +8076,7 @@
       <c r="G149" s="17"/>
     </row>
     <row r="150" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B150" s="34"/>
+      <c r="B150" s="35"/>
       <c r="C150" s="10">
         <v>10</v>
       </c>
@@ -8089,7 +8092,7 @@
       <c r="G150" s="17"/>
     </row>
     <row r="151" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B151" s="35"/>
+      <c r="B151" s="36"/>
       <c r="C151" s="10">
         <v>11</v>
       </c>
@@ -8105,7 +8108,7 @@
       <c r="G151" s="17"/>
     </row>
     <row r="152" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B152" s="33">
+      <c r="B152" s="34">
         <f>SUM(F152:F159)</f>
         <v>361</v>
       </c>
@@ -8124,7 +8127,7 @@
       <c r="G152" s="17"/>
     </row>
     <row r="153" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B153" s="34"/>
+      <c r="B153" s="35"/>
       <c r="C153" s="10">
         <v>2</v>
       </c>
@@ -8140,7 +8143,7 @@
       <c r="G153" s="17"/>
     </row>
     <row r="154" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B154" s="34"/>
+      <c r="B154" s="35"/>
       <c r="C154" s="10">
         <v>3</v>
       </c>
@@ -8156,7 +8159,7 @@
       <c r="G154" s="17"/>
     </row>
     <row r="155" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B155" s="34"/>
+      <c r="B155" s="35"/>
       <c r="C155" s="10">
         <v>4</v>
       </c>
@@ -8172,7 +8175,7 @@
       <c r="G155" s="17"/>
     </row>
     <row r="156" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B156" s="34"/>
+      <c r="B156" s="35"/>
       <c r="C156" s="10">
         <v>5</v>
       </c>
@@ -8188,7 +8191,7 @@
       <c r="G156" s="17"/>
     </row>
     <row r="157" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B157" s="34"/>
+      <c r="B157" s="35"/>
       <c r="C157" s="10">
         <v>6</v>
       </c>
@@ -8204,7 +8207,7 @@
       <c r="G157" s="17"/>
     </row>
     <row r="158" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B158" s="34"/>
+      <c r="B158" s="35"/>
       <c r="C158" s="10">
         <v>7</v>
       </c>
@@ -8220,7 +8223,7 @@
       <c r="G158" s="17"/>
     </row>
     <row r="159" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B159" s="34"/>
+      <c r="B159" s="35"/>
       <c r="C159" s="10">
         <v>8</v>
       </c>
@@ -8236,7 +8239,7 @@
       <c r="G159" s="17"/>
     </row>
     <row r="160" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B160" s="33">
+      <c r="B160" s="34">
         <f>SUM(F160:F165)</f>
         <v>254</v>
       </c>
@@ -8255,7 +8258,7 @@
       <c r="G160" s="17"/>
     </row>
     <row r="161" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B161" s="34"/>
+      <c r="B161" s="35"/>
       <c r="C161" s="10">
         <v>2</v>
       </c>
@@ -8271,7 +8274,7 @@
       <c r="G161" s="17"/>
     </row>
     <row r="162" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B162" s="34"/>
+      <c r="B162" s="35"/>
       <c r="C162" s="10">
         <v>3</v>
       </c>
@@ -8287,7 +8290,7 @@
       <c r="G162" s="17"/>
     </row>
     <row r="163" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B163" s="34"/>
+      <c r="B163" s="35"/>
       <c r="C163" s="10">
         <v>4</v>
       </c>
@@ -8303,7 +8306,7 @@
       <c r="G163" s="17"/>
     </row>
     <row r="164" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B164" s="34"/>
+      <c r="B164" s="35"/>
       <c r="C164" s="10">
         <v>5</v>
       </c>
@@ -8319,7 +8322,7 @@
       <c r="G164" s="17"/>
     </row>
     <row r="165" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B165" s="34"/>
+      <c r="B165" s="35"/>
       <c r="C165" s="10">
         <v>6</v>
       </c>
@@ -8335,7 +8338,7 @@
       <c r="G165" s="17"/>
     </row>
     <row r="166" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B166" s="33">
+      <c r="B166" s="34">
         <f>SUM(F166:F173)</f>
         <v>301</v>
       </c>
@@ -8354,7 +8357,7 @@
       <c r="G166" s="17"/>
     </row>
     <row r="167" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B167" s="34"/>
+      <c r="B167" s="35"/>
       <c r="C167" s="10">
         <v>2</v>
       </c>
@@ -8370,7 +8373,7 @@
       <c r="G167" s="17"/>
     </row>
     <row r="168" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B168" s="34"/>
+      <c r="B168" s="35"/>
       <c r="C168" s="10">
         <v>3</v>
       </c>
@@ -8386,7 +8389,7 @@
       <c r="G168" s="17"/>
     </row>
     <row r="169" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B169" s="34"/>
+      <c r="B169" s="35"/>
       <c r="C169" s="10">
         <v>4</v>
       </c>
@@ -8402,7 +8405,7 @@
       <c r="G169" s="17"/>
     </row>
     <row r="170" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B170" s="34"/>
+      <c r="B170" s="35"/>
       <c r="C170" s="10">
         <v>5</v>
       </c>
@@ -8418,7 +8421,7 @@
       <c r="G170" s="17"/>
     </row>
     <row r="171" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B171" s="34"/>
+      <c r="B171" s="35"/>
       <c r="C171" s="10">
         <v>6</v>
       </c>
@@ -8434,7 +8437,7 @@
       <c r="G171" s="17"/>
     </row>
     <row r="172" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B172" s="34"/>
+      <c r="B172" s="35"/>
       <c r="C172" s="10">
         <v>7</v>
       </c>
@@ -8450,7 +8453,7 @@
       <c r="G172" s="17"/>
     </row>
     <row r="173" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B173" s="35"/>
+      <c r="B173" s="36"/>
       <c r="C173" s="10">
         <v>8</v>
       </c>
@@ -8466,7 +8469,7 @@
       <c r="G173" s="17"/>
     </row>
     <row r="174" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B174" s="33">
+      <c r="B174" s="34">
         <f>SUM(F174:F176)</f>
         <v>250</v>
       </c>
@@ -8485,7 +8488,7 @@
       <c r="G174" s="17"/>
     </row>
     <row r="175" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B175" s="34"/>
+      <c r="B175" s="35"/>
       <c r="C175" s="10">
         <v>2</v>
       </c>
@@ -8501,7 +8504,7 @@
       <c r="G175" s="17"/>
     </row>
     <row r="176" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B176" s="34"/>
+      <c r="B176" s="35"/>
       <c r="C176" s="10">
         <v>3</v>
       </c>
@@ -8517,7 +8520,7 @@
       <c r="G176" s="17"/>
     </row>
     <row r="177" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B177" s="33">
+      <c r="B177" s="34">
         <f>SUM(F177:F178)</f>
         <v>190</v>
       </c>
@@ -8536,7 +8539,7 @@
       <c r="G177" s="17"/>
     </row>
     <row r="178" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B178" s="34"/>
+      <c r="B178" s="35"/>
       <c r="C178" s="10">
         <v>2</v>
       </c>
@@ -8552,7 +8555,7 @@
       <c r="G178" s="17"/>
     </row>
     <row r="179" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B179" s="33">
+      <c r="B179" s="34">
         <f>SUM(F179:F184)</f>
         <v>285</v>
       </c>
@@ -8571,7 +8574,7 @@
       <c r="G179" s="17"/>
     </row>
     <row r="180" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B180" s="34"/>
+      <c r="B180" s="35"/>
       <c r="C180" s="10">
         <v>2</v>
       </c>
@@ -8587,7 +8590,7 @@
       <c r="G180" s="17"/>
     </row>
     <row r="181" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B181" s="34"/>
+      <c r="B181" s="35"/>
       <c r="C181" s="10">
         <v>3</v>
       </c>
@@ -8603,7 +8606,7 @@
       <c r="G181" s="17"/>
     </row>
     <row r="182" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B182" s="34"/>
+      <c r="B182" s="35"/>
       <c r="C182" s="10">
         <v>4</v>
       </c>
@@ -8619,7 +8622,7 @@
       <c r="G182" s="17"/>
     </row>
     <row r="183" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B183" s="34"/>
+      <c r="B183" s="35"/>
       <c r="C183" s="10">
         <v>5</v>
       </c>
@@ -8635,7 +8638,7 @@
       <c r="G183" s="17"/>
     </row>
     <row r="184" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B184" s="34"/>
+      <c r="B184" s="35"/>
       <c r="C184" s="10">
         <v>6</v>
       </c>
@@ -8651,7 +8654,7 @@
       <c r="G184" s="17"/>
     </row>
     <row r="185" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B185" s="33">
+      <c r="B185" s="34">
         <f>SUM(F185:F187)</f>
         <v>138</v>
       </c>
@@ -8670,7 +8673,7 @@
       <c r="G185" s="17"/>
     </row>
     <row r="186" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B186" s="34"/>
+      <c r="B186" s="35"/>
       <c r="C186" s="10">
         <v>2</v>
       </c>
@@ -8686,7 +8689,7 @@
       <c r="G186" s="17"/>
     </row>
     <row r="187" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B187" s="34"/>
+      <c r="B187" s="35"/>
       <c r="C187" s="10">
         <v>3</v>
       </c>
@@ -8721,7 +8724,7 @@
       <c r="G188" s="17"/>
     </row>
     <row r="189" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B189" s="33">
+      <c r="B189" s="34">
         <f>SUM(F189:F191)</f>
         <v>130</v>
       </c>
@@ -8740,7 +8743,7 @@
       <c r="G189" s="17"/>
     </row>
     <row r="190" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B190" s="34"/>
+      <c r="B190" s="35"/>
       <c r="C190" s="10">
         <v>2</v>
       </c>
@@ -8756,7 +8759,7 @@
       <c r="G190" s="17"/>
     </row>
     <row r="191" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B191" s="34"/>
+      <c r="B191" s="35"/>
       <c r="C191" s="10">
         <v>3</v>
       </c>
@@ -8772,7 +8775,7 @@
       <c r="G191" s="17"/>
     </row>
     <row r="192" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B192" s="33">
+      <c r="B192" s="34">
         <f>SUM(F192:F193)</f>
         <v>130</v>
       </c>
@@ -8791,7 +8794,7 @@
       <c r="G192" s="17"/>
     </row>
     <row r="193" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B193" s="34"/>
+      <c r="B193" s="35"/>
       <c r="C193" s="10">
         <v>2</v>
       </c>
@@ -8807,7 +8810,7 @@
       <c r="G193" s="17"/>
     </row>
     <row r="194" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B194" s="33">
+      <c r="B194" s="34">
         <f>SUM(F192:F193)</f>
         <v>130</v>
       </c>
@@ -8826,7 +8829,7 @@
       <c r="G194" s="19"/>
     </row>
     <row r="195" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B195" s="35"/>
+      <c r="B195" s="36"/>
       <c r="C195" s="5">
         <v>2</v>
       </c>
@@ -8861,7 +8864,7 @@
       <c r="G196" s="17"/>
     </row>
     <row r="197" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B197" s="33">
+      <c r="B197" s="34">
         <f>SUM(F197:F198)</f>
         <v>160</v>
       </c>
@@ -8880,7 +8883,7 @@
       <c r="G197" s="17"/>
     </row>
     <row r="198" spans="2:7" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B198" s="35"/>
+      <c r="B198" s="36"/>
       <c r="C198" s="10">
         <v>2</v>
       </c>
@@ -8896,7 +8899,7 @@
       <c r="G198" s="17"/>
     </row>
     <row r="199" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B199" s="33">
+      <c r="B199" s="34">
         <f>SUM(F199:F202)</f>
         <v>225</v>
       </c>
@@ -8915,7 +8918,7 @@
       <c r="G199" s="17"/>
     </row>
     <row r="200" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B200" s="34"/>
+      <c r="B200" s="35"/>
       <c r="C200" s="10">
         <v>2</v>
       </c>
@@ -8931,7 +8934,7 @@
       <c r="G200" s="17"/>
     </row>
     <row r="201" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B201" s="34"/>
+      <c r="B201" s="35"/>
       <c r="C201" s="10">
         <v>3</v>
       </c>
@@ -8947,7 +8950,7 @@
       <c r="G201" s="17"/>
     </row>
     <row r="202" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B202" s="34"/>
+      <c r="B202" s="35"/>
       <c r="C202" s="10">
         <v>4</v>
       </c>
@@ -8963,7 +8966,7 @@
       <c r="G202" s="17"/>
     </row>
     <row r="203" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B203" s="43">
+      <c r="B203" s="44">
         <f>SUM(F203:F204)</f>
         <v>120</v>
       </c>
@@ -8982,7 +8985,7 @@
       <c r="G203" s="19"/>
     </row>
     <row r="204" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B204" s="44"/>
+      <c r="B204" s="45"/>
       <c r="C204" s="10">
         <v>2</v>
       </c>
@@ -9012,6 +9015,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B54:B67"/>
+    <mergeCell ref="B68:B75"/>
+    <mergeCell ref="B76:B85"/>
+    <mergeCell ref="B86:B95"/>
+    <mergeCell ref="B96:B102"/>
+    <mergeCell ref="D1:F2"/>
+    <mergeCell ref="B19:B26"/>
+    <mergeCell ref="B27:B38"/>
+    <mergeCell ref="B39:B45"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="B152:B159"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B197:B198"/>
+    <mergeCell ref="B199:B202"/>
+    <mergeCell ref="B103:B111"/>
     <mergeCell ref="B203:B204"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B189:B191"/>
@@ -9028,21 +9046,6 @@
     <mergeCell ref="B125:B128"/>
     <mergeCell ref="B129:B140"/>
     <mergeCell ref="B141:B151"/>
-    <mergeCell ref="B152:B159"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B197:B198"/>
-    <mergeCell ref="B199:B202"/>
-    <mergeCell ref="B103:B111"/>
-    <mergeCell ref="D1:F2"/>
-    <mergeCell ref="B19:B26"/>
-    <mergeCell ref="B27:B38"/>
-    <mergeCell ref="B39:B45"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="B54:B67"/>
-    <mergeCell ref="B68:B75"/>
-    <mergeCell ref="B76:B85"/>
-    <mergeCell ref="B86:B95"/>
-    <mergeCell ref="B96:B102"/>
   </mergeCells>
   <conditionalFormatting sqref="F67:F92 F1:F18 F20:F61 F95:F100 F102:F1048576">
     <cfRule type="cellIs" dxfId="60" priority="19" operator="between">
@@ -9180,20 +9183,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="22.5" customHeight="1">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="36">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="37">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="36"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
       <c r="C3" s="15" t="s">
@@ -9257,7 +9260,7 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>SUM(E6:E12)</f>
         <v>270</v>
       </c>
@@ -9279,7 +9282,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="4">
         <v>45957</v>
       </c>
@@ -9298,7 +9301,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="4">
         <v>45957</v>
       </c>
@@ -9317,7 +9320,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="4">
         <v>45957</v>
       </c>
@@ -9336,7 +9339,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="4">
         <v>45957</v>
       </c>
@@ -9355,7 +9358,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="4">
         <v>45957</v>
       </c>
@@ -9374,7 +9377,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B12" s="35"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="4">
         <v>45957</v>
       </c>
@@ -9415,7 +9418,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>SUM(E14:E15)</f>
         <v>280</v>
       </c>
@@ -9437,7 +9440,7 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B15" s="35"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="4">
         <v>45959</v>
       </c>
@@ -9456,7 +9459,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>SUM(E16:E18)</f>
         <v>85</v>
       </c>
@@ -9478,7 +9481,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B17" s="34"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="4">
         <v>45960</v>
       </c>
@@ -9497,7 +9500,7 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B18" s="35"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="4">
         <v>45960</v>
       </c>
@@ -9516,7 +9519,7 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B19" s="33">
+      <c r="B19" s="34">
         <f>SUM(E19:E21)</f>
         <v>240</v>
       </c>
@@ -9538,7 +9541,7 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B20" s="34"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="4">
         <v>45961</v>
       </c>
@@ -9557,7 +9560,7 @@
       </c>
     </row>
     <row r="21" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B21" s="34"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="4">
         <v>45961</v>
       </c>
@@ -9598,7 +9601,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B23" s="33">
+      <c r="B23" s="34">
         <f>SUM(E23:E24)</f>
         <v>150</v>
       </c>
@@ -9620,7 +9623,7 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B24" s="35"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="4">
         <v>45963</v>
       </c>
@@ -9639,7 +9642,7 @@
       </c>
     </row>
     <row r="25" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B25" s="34">
+      <c r="B25" s="35">
         <f>SUM(E25:E27)</f>
         <v>270</v>
       </c>
@@ -9661,7 +9664,7 @@
       </c>
     </row>
     <row r="26" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B26" s="34"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="4">
         <v>45964</v>
       </c>
@@ -9680,7 +9683,7 @@
       </c>
     </row>
     <row r="27" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B27" s="34"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="4">
         <v>45964</v>
       </c>
@@ -9699,7 +9702,7 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B28" s="33">
+      <c r="B28" s="34">
         <f>SUM(E28:E29)</f>
         <v>110</v>
       </c>
@@ -9721,7 +9724,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="4">
         <v>45965</v>
       </c>
@@ -9740,7 +9743,7 @@
       </c>
     </row>
     <row r="30" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <f>SUM(E30:E31)</f>
         <v>110</v>
       </c>
@@ -9762,7 +9765,7 @@
       </c>
     </row>
     <row r="31" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4">
         <v>45966</v>
       </c>
@@ -9781,7 +9784,7 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <f>SUM(E32:E33)</f>
         <v>115</v>
       </c>
@@ -9803,7 +9806,7 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B33" s="35"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="4">
         <v>45967</v>
       </c>
@@ -9822,7 +9825,7 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <f>SUM(E34:E36)</f>
         <v>350</v>
       </c>
@@ -9844,7 +9847,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="4">
         <v>45968</v>
       </c>
@@ -9857,7 +9860,7 @@
       <c r="F35" s="17"/>
     </row>
     <row r="36" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B36" s="35"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="4">
         <v>45968</v>
       </c>
@@ -9886,7 +9889,7 @@
       <c r="F37" s="17"/>
     </row>
     <row r="38" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B38" s="33">
+      <c r="B38" s="34">
         <f>SUM(E38:E39)</f>
         <v>120</v>
       </c>
@@ -9902,7 +9905,7 @@
       <c r="F38" s="17"/>
     </row>
     <row r="39" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B39" s="34"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="4">
         <v>45970</v>
       </c>
@@ -9931,7 +9934,7 @@
       <c r="F40" s="17"/>
     </row>
     <row r="41" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B41" s="33">
+      <c r="B41" s="34">
         <f>SUM(E41:E42)</f>
         <v>120</v>
       </c>
@@ -9947,7 +9950,7 @@
       <c r="F41" s="17"/>
     </row>
     <row r="42" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B42" s="34"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="4">
         <v>45972</v>
       </c>
@@ -9960,7 +9963,7 @@
       <c r="F42" s="17"/>
     </row>
     <row r="43" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B43" s="33">
+      <c r="B43" s="34">
         <f>SUM(E43:E44)</f>
         <v>120</v>
       </c>
@@ -9976,7 +9979,7 @@
       <c r="F43" s="17"/>
     </row>
     <row r="44" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B44" s="34"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="4">
         <v>45973</v>
       </c>
@@ -9989,7 +9992,7 @@
       <c r="F44" s="17"/>
     </row>
     <row r="45" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B45" s="33">
+      <c r="B45" s="34">
         <f>SUM(E45:E46)</f>
         <v>120</v>
       </c>
@@ -10005,7 +10008,7 @@
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B46" s="34"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="4">
         <v>45974</v>
       </c>
@@ -10018,7 +10021,7 @@
       <c r="F46" s="17"/>
     </row>
     <row r="47" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B47" s="33">
+      <c r="B47" s="34">
         <f>SUM(E47:E48)</f>
         <v>120</v>
       </c>
@@ -10034,7 +10037,7 @@
       <c r="F47" s="17"/>
     </row>
     <row r="48" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B48" s="34"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="4">
         <v>45975</v>
       </c>
@@ -10047,7 +10050,7 @@
       <c r="F48" s="17"/>
     </row>
     <row r="49" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B49" s="33">
+      <c r="B49" s="34">
         <f>SUM(E49:E51)</f>
         <v>215</v>
       </c>
@@ -10063,7 +10066,7 @@
       <c r="F49" s="17"/>
     </row>
     <row r="50" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B50" s="34"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="4">
         <v>45976</v>
       </c>
@@ -10076,7 +10079,7 @@
       <c r="F50" s="17"/>
     </row>
     <row r="51" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B51" s="34"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="4">
         <v>45976</v>
       </c>
@@ -10089,7 +10092,7 @@
       <c r="F51" s="17"/>
     </row>
     <row r="52" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B52" s="33">
+      <c r="B52" s="34">
         <f>SUM(E52:E54)</f>
         <v>300</v>
       </c>
@@ -10105,7 +10108,7 @@
       <c r="F52" s="17"/>
     </row>
     <row r="53" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B53" s="34"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="4">
         <v>45977</v>
       </c>
@@ -10118,7 +10121,7 @@
       <c r="F53" s="17"/>
     </row>
     <row r="54" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B54" s="34"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="4">
         <v>45977</v>
       </c>
@@ -10131,7 +10134,7 @@
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B55" s="33">
+      <c r="B55" s="34">
         <f>SUM(E55:E59)</f>
         <v>250</v>
       </c>
@@ -10147,7 +10150,7 @@
       <c r="F55" s="17"/>
     </row>
     <row r="56" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B56" s="34"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="4">
         <v>45978</v>
       </c>
@@ -10160,7 +10163,7 @@
       <c r="F56" s="17"/>
     </row>
     <row r="57" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B57" s="34"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="4">
         <v>45978</v>
       </c>
@@ -10173,7 +10176,7 @@
       <c r="F57" s="17"/>
     </row>
     <row r="58" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B58" s="34"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="4">
         <v>45978</v>
       </c>
@@ -10186,7 +10189,7 @@
       <c r="F58" s="17"/>
     </row>
     <row r="59" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B59" s="35"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="4">
         <v>45978</v>
       </c>
@@ -10215,7 +10218,7 @@
       <c r="F60" s="17"/>
     </row>
     <row r="61" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B61" s="33">
+      <c r="B61" s="34">
         <f>SUM(E61:E62)</f>
         <v>50</v>
       </c>
@@ -10231,7 +10234,7 @@
       <c r="F61" s="17"/>
     </row>
     <row r="62" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B62" s="34"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="4">
         <v>45980</v>
       </c>
@@ -10244,7 +10247,7 @@
       <c r="F62" s="17"/>
     </row>
     <row r="63" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B63" s="33">
+      <c r="B63" s="34">
         <f>SUM(E63:E69)</f>
         <v>300</v>
       </c>
@@ -10260,7 +10263,7 @@
       <c r="F63" s="17"/>
     </row>
     <row r="64" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B64" s="34"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="4">
         <v>45981</v>
       </c>
@@ -10273,7 +10276,7 @@
       <c r="F64" s="17"/>
     </row>
     <row r="65" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B65" s="34"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="4">
         <v>45981</v>
       </c>
@@ -10286,7 +10289,7 @@
       <c r="F65" s="17"/>
     </row>
     <row r="66" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B66" s="34"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="4">
         <v>45981</v>
       </c>
@@ -10299,7 +10302,7 @@
       <c r="F66" s="17"/>
     </row>
     <row r="67" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B67" s="34"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="4">
         <v>45981</v>
       </c>
@@ -10312,7 +10315,7 @@
       <c r="F67" s="17"/>
     </row>
     <row r="68" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B68" s="34"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="4">
         <v>45981</v>
       </c>
@@ -10325,7 +10328,7 @@
       <c r="F68" s="17"/>
     </row>
     <row r="69" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B69" s="35"/>
+      <c r="B69" s="36"/>
       <c r="C69" s="4">
         <v>45981</v>
       </c>
@@ -10338,7 +10341,7 @@
       <c r="F69" s="17"/>
     </row>
     <row r="70" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B70" s="33">
+      <c r="B70" s="34">
         <f>SUM(E70:E72)</f>
         <v>165</v>
       </c>
@@ -10354,7 +10357,7 @@
       <c r="F70" s="17"/>
     </row>
     <row r="71" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B71" s="34"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="4">
         <v>45982</v>
       </c>
@@ -10367,7 +10370,7 @@
       <c r="F71" s="17"/>
     </row>
     <row r="72" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B72" s="34"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="4">
         <v>45982</v>
       </c>
@@ -10380,7 +10383,7 @@
       <c r="F72" s="17"/>
     </row>
     <row r="73" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B73" s="33">
+      <c r="B73" s="34">
         <f>SUM(E73:E78)</f>
         <v>200</v>
       </c>
@@ -10396,7 +10399,7 @@
       <c r="F73" s="17"/>
     </row>
     <row r="74" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B74" s="34"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="4">
         <v>45983</v>
       </c>
@@ -10409,7 +10412,7 @@
       <c r="F74" s="17"/>
     </row>
     <row r="75" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B75" s="34"/>
+      <c r="B75" s="35"/>
       <c r="C75" s="4">
         <v>45983</v>
       </c>
@@ -10422,7 +10425,7 @@
       <c r="F75" s="17"/>
     </row>
     <row r="76" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B76" s="34"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="4">
         <v>45983</v>
       </c>
@@ -10435,7 +10438,7 @@
       <c r="F76" s="17"/>
     </row>
     <row r="77" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B77" s="34"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="4">
         <v>45983</v>
       </c>
@@ -10448,7 +10451,7 @@
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B78" s="35"/>
+      <c r="B78" s="36"/>
       <c r="C78" s="4">
         <v>45983</v>
       </c>
@@ -10461,7 +10464,7 @@
       <c r="F78" s="17"/>
     </row>
     <row r="79" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B79" s="33">
+      <c r="B79" s="34">
         <f>SUM(E79:E84)</f>
         <v>320</v>
       </c>
@@ -10477,7 +10480,7 @@
       <c r="F79" s="19"/>
     </row>
     <row r="80" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B80" s="34"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="4">
         <v>45984</v>
       </c>
@@ -10490,7 +10493,7 @@
       <c r="F80" s="19"/>
     </row>
     <row r="81" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B81" s="34"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="4">
         <v>45984</v>
       </c>
@@ -10503,7 +10506,7 @@
       <c r="F81" s="17"/>
     </row>
     <row r="82" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B82" s="34"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="4">
         <v>45984</v>
       </c>
@@ -10516,7 +10519,7 @@
       <c r="F82" s="17"/>
     </row>
     <row r="83" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="4">
         <v>45984</v>
       </c>
@@ -10529,7 +10532,7 @@
       <c r="F83" s="17"/>
     </row>
     <row r="84" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="4">
         <v>45984</v>
       </c>
@@ -10542,7 +10545,7 @@
       <c r="F84" s="17"/>
     </row>
     <row r="85" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B85" s="35"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="4">
         <v>45984</v>
       </c>
@@ -10555,7 +10558,7 @@
       <c r="F85" s="17"/>
     </row>
     <row r="86" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B86" s="33">
+      <c r="B86" s="34">
         <f>SUM(E86:E87)</f>
         <v>130</v>
       </c>
@@ -10571,7 +10574,7 @@
       <c r="F86" s="17"/>
     </row>
     <row r="87" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B87" s="35"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="4">
         <v>45985</v>
       </c>
@@ -10584,7 +10587,7 @@
       <c r="F87" s="17"/>
     </row>
     <row r="88" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B88" s="33">
+      <c r="B88" s="34">
         <f>SUM(E88:E89)</f>
         <v>150</v>
       </c>
@@ -10600,7 +10603,7 @@
       <c r="F88" s="17"/>
     </row>
     <row r="89" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B89" s="34"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="4">
         <v>45986</v>
       </c>
@@ -10613,7 +10616,7 @@
       <c r="F89" s="17"/>
     </row>
     <row r="90" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B90" s="34"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="4">
         <v>45986</v>
       </c>
@@ -10626,14 +10629,14 @@
       <c r="F90" s="17"/>
     </row>
     <row r="91" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B91" s="34"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="4"/>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="17"/>
     </row>
     <row r="92" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B92" s="43">
+      <c r="B92" s="44">
         <f>SUM(E92:E93)</f>
         <v>0</v>
       </c>
@@ -10643,7 +10646,7 @@
       <c r="F92" s="19"/>
     </row>
     <row r="93" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B93" s="44"/>
+      <c r="B93" s="45"/>
       <c r="C93" s="4"/>
       <c r="D93" s="12"/>
       <c r="E93" s="12"/>
@@ -10657,27 +10660,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="B88:B91"/>
-    <mergeCell ref="B73:B78"/>
-    <mergeCell ref="B79:B85"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="B63:B69"/>
-    <mergeCell ref="C1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B32:B33"/>
@@ -10685,6 +10667,27 @@
     <mergeCell ref="B6:B12"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B63:B69"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="B88:B91"/>
+    <mergeCell ref="B73:B78"/>
+    <mergeCell ref="B79:B85"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:E18 E86:E1048576 E20:E84">
     <cfRule type="cellIs" dxfId="35" priority="25" operator="between">
@@ -10735,20 +10738,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="22.5" customHeight="1">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="36">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="37">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="36"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
       <c r="C3" s="15" t="s">
@@ -10765,7 +10768,7 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>SUM(E4:E5)</f>
         <v>80</v>
       </c>
@@ -10790,7 +10793,7 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="4">
         <v>45986</v>
       </c>
@@ -10809,7 +10812,7 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>SUM(E6:E10)</f>
         <v>180</v>
       </c>
@@ -10831,7 +10834,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="4">
         <v>45987</v>
       </c>
@@ -10850,7 +10853,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="4">
         <v>45987</v>
       </c>
@@ -10869,7 +10872,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="4">
         <v>45987</v>
       </c>
@@ -10888,7 +10891,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="4">
         <v>45987</v>
       </c>
@@ -10907,7 +10910,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B11" s="33">
+      <c r="B11" s="34">
         <f>SUM(E11:E13)</f>
         <v>230</v>
       </c>
@@ -10929,7 +10932,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="4">
         <v>45988</v>
       </c>
@@ -10948,7 +10951,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B13" s="35"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="4">
         <v>45988</v>
       </c>
@@ -10967,7 +10970,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>SUM(E14:E18)</f>
         <v>250</v>
       </c>
@@ -10989,7 +10992,7 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B15" s="34"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="4">
         <v>45989</v>
       </c>
@@ -11008,7 +11011,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B16" s="34"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="4">
         <v>45989</v>
       </c>
@@ -11027,7 +11030,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B17" s="34"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="4">
         <v>45989</v>
       </c>
@@ -11046,7 +11049,7 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B18" s="34"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="4">
         <v>45989</v>
       </c>
@@ -11065,7 +11068,7 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B19" s="33">
+      <c r="B19" s="34">
         <f>SUM(E19:E21)</f>
         <v>75</v>
       </c>
@@ -11087,7 +11090,7 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B20" s="34"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="4">
         <v>45990</v>
       </c>
@@ -11106,7 +11109,7 @@
       </c>
     </row>
     <row r="21" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B21" s="34"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="4">
         <v>45990</v>
       </c>
@@ -11125,7 +11128,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B22" s="33">
+      <c r="B22" s="34">
         <f>SUM(E22:E23)</f>
         <v>80</v>
       </c>
@@ -11147,7 +11150,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B23" s="35"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="4">
         <v>45991</v>
       </c>
@@ -11166,7 +11169,7 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B24" s="33">
+      <c r="B24" s="34">
         <f>SUM(E24:E26)</f>
         <v>120</v>
       </c>
@@ -11188,7 +11191,7 @@
       </c>
     </row>
     <row r="25" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="4">
         <v>45992</v>
       </c>
@@ -11207,7 +11210,7 @@
       </c>
     </row>
     <row r="26" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B26" s="35"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="4">
         <v>45992</v>
       </c>
@@ -11226,7 +11229,7 @@
       </c>
     </row>
     <row r="27" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B27" s="34">
+      <c r="B27" s="35">
         <f>SUM(E27:E29)</f>
         <v>190</v>
       </c>
@@ -11248,7 +11251,7 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B28" s="34"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="4">
         <v>45993</v>
       </c>
@@ -11267,7 +11270,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="4">
         <v>45993</v>
       </c>
@@ -11308,7 +11311,7 @@
       </c>
     </row>
     <row r="31" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <f>SUM(E31:E36)</f>
         <v>416</v>
       </c>
@@ -11330,7 +11333,7 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4">
         <v>45995</v>
       </c>
@@ -11346,7 +11349,7 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="4">
         <v>45995</v>
       </c>
@@ -11359,7 +11362,7 @@
       <c r="F33" s="17"/>
     </row>
     <row r="34" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="4">
         <v>45995</v>
       </c>
@@ -11372,7 +11375,7 @@
       <c r="F34" s="17"/>
     </row>
     <row r="35" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="4">
         <v>45995</v>
       </c>
@@ -11385,7 +11388,7 @@
       <c r="F35" s="17"/>
     </row>
     <row r="36" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4">
         <v>45995</v>
       </c>
@@ -11420,7 +11423,7 @@
       <c r="F37" s="17"/>
     </row>
     <row r="38" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B38" s="33">
+      <c r="B38" s="34">
         <f>SUM(E38:E43)</f>
         <v>240</v>
       </c>
@@ -11436,7 +11439,7 @@
       <c r="F38" s="17"/>
     </row>
     <row r="39" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B39" s="34"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="4">
         <v>45997</v>
       </c>
@@ -11449,7 +11452,7 @@
       <c r="F39" s="17"/>
     </row>
     <row r="40" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B40" s="34"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="4">
         <v>45997</v>
       </c>
@@ -11462,7 +11465,7 @@
       <c r="F40" s="17"/>
     </row>
     <row r="41" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B41" s="34"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="4">
         <v>45997</v>
       </c>
@@ -11475,7 +11478,7 @@
       <c r="F41" s="17"/>
     </row>
     <row r="42" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B42" s="34"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="4">
         <v>45997</v>
       </c>
@@ -11488,7 +11491,7 @@
       <c r="F42" s="17"/>
     </row>
     <row r="43" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B43" s="35"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="4">
         <v>45997</v>
       </c>
@@ -11501,7 +11504,7 @@
       <c r="F43" s="17"/>
     </row>
     <row r="44" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B44" s="33">
+      <c r="B44" s="34">
         <f>SUM(E44:E47)</f>
         <v>150</v>
       </c>
@@ -11517,7 +11520,7 @@
       <c r="F44" s="17"/>
     </row>
     <row r="45" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B45" s="34"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="4">
         <v>45998</v>
       </c>
@@ -11530,7 +11533,7 @@
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B46" s="34"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="4">
         <v>45998</v>
       </c>
@@ -11543,7 +11546,7 @@
       <c r="F46" s="17"/>
     </row>
     <row r="47" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B47" s="35"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="4">
         <v>45998</v>
       </c>
@@ -11572,7 +11575,7 @@
       <c r="F48" s="17"/>
     </row>
     <row r="49" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B49" s="33">
+      <c r="B49" s="34">
         <f>SUM(E49:E50)</f>
         <v>110</v>
       </c>
@@ -11588,7 +11591,7 @@
       <c r="F49" s="17"/>
     </row>
     <row r="50" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B50" s="35"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="4">
         <v>46000</v>
       </c>
@@ -11601,7 +11604,7 @@
       <c r="F50" s="17"/>
     </row>
     <row r="51" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B51" s="33">
+      <c r="B51" s="34">
         <f>SUM(E51:E56)</f>
         <v>280</v>
       </c>
@@ -11617,7 +11620,7 @@
       <c r="F51" s="17"/>
     </row>
     <row r="52" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B52" s="34"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="4">
         <v>46001</v>
       </c>
@@ -11630,7 +11633,7 @@
       <c r="F52" s="17"/>
     </row>
     <row r="53" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B53" s="34"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="4">
         <v>46001</v>
       </c>
@@ -11643,7 +11646,7 @@
       <c r="F53" s="17"/>
     </row>
     <row r="54" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B54" s="34"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="4">
         <v>46001</v>
       </c>
@@ -11656,7 +11659,7 @@
       <c r="F54" s="17"/>
     </row>
     <row r="55" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B55" s="34"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="4">
         <v>46001</v>
       </c>
@@ -11669,7 +11672,7 @@
       <c r="F55" s="17"/>
     </row>
     <row r="56" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B56" s="35"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="4">
         <v>46001</v>
       </c>
@@ -11682,7 +11685,7 @@
       <c r="F56" s="17"/>
     </row>
     <row r="57" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B57" s="33">
+      <c r="B57" s="34">
         <f>SUM(E57:E60)</f>
         <v>200</v>
       </c>
@@ -11698,7 +11701,7 @@
       <c r="F57" s="17"/>
     </row>
     <row r="58" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B58" s="34"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="4">
         <v>46002</v>
       </c>
@@ -11711,7 +11714,7 @@
       <c r="F58" s="17"/>
     </row>
     <row r="59" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B59" s="34"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="4">
         <v>46002</v>
       </c>
@@ -11724,7 +11727,7 @@
       <c r="F59" s="17"/>
     </row>
     <row r="60" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B60" s="34"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="4">
         <v>46002</v>
       </c>
@@ -11737,7 +11740,7 @@
       <c r="F60" s="17"/>
     </row>
     <row r="61" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B61" s="33">
+      <c r="B61" s="34">
         <f>SUM(E61:E62)</f>
         <v>120</v>
       </c>
@@ -11753,7 +11756,7 @@
       <c r="F61" s="17"/>
     </row>
     <row r="62" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B62" s="34"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="4">
         <v>46003</v>
       </c>
@@ -11766,7 +11769,7 @@
       <c r="F62" s="17"/>
     </row>
     <row r="63" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B63" s="33">
+      <c r="B63" s="34">
         <f>SUM(E63:E66)</f>
         <v>160</v>
       </c>
@@ -11782,7 +11785,7 @@
       <c r="F63" s="17"/>
     </row>
     <row r="64" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B64" s="34"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="4">
         <v>46004</v>
       </c>
@@ -11795,7 +11798,7 @@
       <c r="F64" s="17"/>
     </row>
     <row r="65" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B65" s="34"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="4">
         <v>46004</v>
       </c>
@@ -11808,7 +11811,7 @@
       <c r="F65" s="17"/>
     </row>
     <row r="66" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B66" s="35"/>
+      <c r="B66" s="36"/>
       <c r="C66" s="4">
         <v>46004</v>
       </c>
@@ -11821,7 +11824,7 @@
       <c r="F66" s="17"/>
     </row>
     <row r="67" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B67" s="33">
+      <c r="B67" s="34">
         <f>SUM(E67:E70)</f>
         <v>245</v>
       </c>
@@ -11837,7 +11840,7 @@
       <c r="F67" s="17"/>
     </row>
     <row r="68" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B68" s="34"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="4">
         <v>46005</v>
       </c>
@@ -11850,7 +11853,7 @@
       <c r="F68" s="17"/>
     </row>
     <row r="69" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B69" s="34"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="4">
         <v>46005</v>
       </c>
@@ -11863,7 +11866,7 @@
       <c r="F69" s="17"/>
     </row>
     <row r="70" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B70" s="34"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="4">
         <v>46005</v>
       </c>
@@ -11892,7 +11895,7 @@
       <c r="F71" s="17"/>
     </row>
     <row r="72" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B72" s="33">
+      <c r="B72" s="34">
         <f>SUM(E72:E74)</f>
         <v>415</v>
       </c>
@@ -11908,7 +11911,7 @@
       <c r="F72" s="17"/>
     </row>
     <row r="73" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B73" s="34"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="4">
         <v>46007</v>
       </c>
@@ -11921,7 +11924,7 @@
       <c r="F73" s="17"/>
     </row>
     <row r="74" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B74" s="34"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="4"/>
       <c r="D74" s="12"/>
       <c r="E74" s="12">
@@ -11930,7 +11933,7 @@
       <c r="F74" s="17"/>
     </row>
     <row r="75" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B75" s="33">
+      <c r="B75" s="34">
         <f>SUM(E75:E79)</f>
         <v>290</v>
       </c>
@@ -11946,7 +11949,7 @@
       <c r="F75" s="17"/>
     </row>
     <row r="76" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B76" s="34"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="4">
         <v>46009</v>
       </c>
@@ -11959,7 +11962,7 @@
       <c r="F76" s="17"/>
     </row>
     <row r="77" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B77" s="34"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="4">
         <v>46009</v>
       </c>
@@ -11972,7 +11975,7 @@
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B78" s="34"/>
+      <c r="B78" s="35"/>
       <c r="C78" s="4">
         <v>46009</v>
       </c>
@@ -11985,7 +11988,7 @@
       <c r="F78" s="17"/>
     </row>
     <row r="79" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B79" s="35"/>
+      <c r="B79" s="36"/>
       <c r="C79" s="4">
         <v>46009</v>
       </c>
@@ -11998,7 +12001,7 @@
       <c r="F79" s="17"/>
     </row>
     <row r="80" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B80" s="33">
+      <c r="B80" s="34">
         <f>SUM(E80:E81)</f>
         <v>140</v>
       </c>
@@ -12017,7 +12020,7 @@
       <c r="A81" s="2">
         <v>4371</v>
       </c>
-      <c r="B81" s="34"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="4">
         <v>46010</v>
       </c>
@@ -12030,7 +12033,7 @@
       <c r="F81" s="17"/>
     </row>
     <row r="82" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B82" s="33">
+      <c r="B82" s="34">
         <f>SUM(E82:E86)</f>
         <v>175</v>
       </c>
@@ -12046,7 +12049,7 @@
       <c r="F82" s="17"/>
     </row>
     <row r="83" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="4">
         <v>46011</v>
       </c>
@@ -12059,7 +12062,7 @@
       <c r="F83" s="17"/>
     </row>
     <row r="84" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="4">
         <v>46011</v>
       </c>
@@ -12072,7 +12075,7 @@
       <c r="F84" s="17"/>
     </row>
     <row r="85" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B85" s="34"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="4">
         <v>46011</v>
       </c>
@@ -12085,7 +12088,7 @@
       <c r="F85" s="17"/>
     </row>
     <row r="86" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B86" s="34"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="4">
         <v>46011</v>
       </c>
@@ -12098,7 +12101,7 @@
       <c r="F86" s="17"/>
     </row>
     <row r="87" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B87" s="33">
+      <c r="B87" s="34">
         <f>SUM(E87:E94)</f>
         <v>235</v>
       </c>
@@ -12114,7 +12117,7 @@
       <c r="F87" s="17"/>
     </row>
     <row r="88" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B88" s="34"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="4">
         <v>46012</v>
       </c>
@@ -12127,7 +12130,7 @@
       <c r="F88" s="17"/>
     </row>
     <row r="89" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B89" s="34"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="4">
         <v>46012</v>
       </c>
@@ -12140,7 +12143,7 @@
       <c r="F89" s="17"/>
     </row>
     <row r="90" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B90" s="34"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="4">
         <v>46012</v>
       </c>
@@ -12153,7 +12156,7 @@
       <c r="F90" s="17"/>
     </row>
     <row r="91" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B91" s="34"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="4">
         <v>46012</v>
       </c>
@@ -12166,7 +12169,7 @@
       <c r="F91" s="17"/>
     </row>
     <row r="92" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B92" s="34"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="4">
         <v>46012</v>
       </c>
@@ -12179,7 +12182,7 @@
       <c r="F92" s="17"/>
     </row>
     <row r="93" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B93" s="34"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="4">
         <v>46012</v>
       </c>
@@ -12192,7 +12195,7 @@
       <c r="F93" s="17"/>
     </row>
     <row r="94" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B94" s="34"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="4">
         <v>46012</v>
       </c>
@@ -12221,7 +12224,7 @@
       <c r="F95" s="17"/>
     </row>
     <row r="96" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B96" s="33">
+      <c r="B96" s="34">
         <f>SUM(E96:E98)</f>
         <v>233</v>
       </c>
@@ -12237,7 +12240,7 @@
       <c r="F96" s="19"/>
     </row>
     <row r="97" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B97" s="34"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="4">
         <v>46014</v>
       </c>
@@ -12250,7 +12253,7 @@
       <c r="F97" s="19"/>
     </row>
     <row r="98" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B98" s="34"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="4">
         <v>46014</v>
       </c>
@@ -12263,7 +12266,7 @@
       <c r="F98" s="17"/>
     </row>
     <row r="99" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B99" s="33">
+      <c r="B99" s="34">
         <f>SUM(E99:E101)</f>
         <v>150</v>
       </c>
@@ -12279,7 +12282,7 @@
       <c r="F99" s="17"/>
     </row>
     <row r="100" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B100" s="34"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="4">
         <v>46015</v>
       </c>
@@ -12292,7 +12295,7 @@
       <c r="F100" s="17"/>
     </row>
     <row r="101" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B101" s="35"/>
+      <c r="B101" s="36"/>
       <c r="C101" s="4">
         <v>46015</v>
       </c>
@@ -12305,7 +12308,7 @@
       <c r="F101" s="17"/>
     </row>
     <row r="102" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B102" s="33">
+      <c r="B102" s="34">
         <f>SUM(E102:E103)</f>
         <v>97</v>
       </c>
@@ -12321,7 +12324,7 @@
       <c r="F102" s="17"/>
     </row>
     <row r="103" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B103" s="34"/>
+      <c r="B103" s="35"/>
       <c r="C103" s="4">
         <v>46016</v>
       </c>
@@ -12334,7 +12337,7 @@
       <c r="F103" s="17"/>
     </row>
     <row r="104" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B104" s="34"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="4">
         <v>46016</v>
       </c>
@@ -12347,7 +12350,7 @@
       <c r="F104" s="17"/>
     </row>
     <row r="105" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B105" s="34"/>
+      <c r="B105" s="35"/>
       <c r="C105" s="4">
         <v>46016</v>
       </c>
@@ -12360,7 +12363,7 @@
       <c r="F105" s="17"/>
     </row>
     <row r="106" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B106" s="43">
+      <c r="B106" s="44">
         <f>SUM(E106:E107)</f>
         <v>-5386</v>
       </c>
@@ -12374,7 +12377,7 @@
       <c r="F106" s="19"/>
     </row>
     <row r="107" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B107" s="44"/>
+      <c r="B107" s="45"/>
       <c r="C107" s="4"/>
       <c r="D107" s="12"/>
       <c r="E107" s="12"/>
@@ -12388,18 +12391,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C1:E2"/>
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="B96:B98"/>
     <mergeCell ref="B99:B101"/>
     <mergeCell ref="B102:B105"/>
@@ -12416,6 +12407,18 @@
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="B57:B60"/>
     <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="B51:B56"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C1:E2"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:E18 E20:E1048576">
     <cfRule type="cellIs" dxfId="23" priority="1" operator="between">
@@ -12456,7 +12459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.5703125" defaultRowHeight="22.5" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="20.5703125" style="2"/>
@@ -12466,20 +12469,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="22.5" customHeight="1">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="36">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="37">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="36"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
       <c r="C3" s="15" t="s">
@@ -12496,7 +12499,7 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>SUM(E4:E5)</f>
         <v>1643</v>
       </c>
@@ -12510,8 +12513,8 @@
         <v>1593</v>
       </c>
       <c r="F4" s="18">
-        <f>SUM(E4:E103)</f>
-        <v>4283</v>
+        <f>SUM(E4:E99)</f>
+        <v>4653</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -12521,7 +12524,7 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="4">
         <v>46031</v>
       </c>
@@ -12540,7 +12543,7 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>SUM(E6:E9)</f>
         <v>175</v>
       </c>
@@ -12562,7 +12565,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="4">
         <v>46032</v>
       </c>
@@ -12581,7 +12584,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="4">
         <v>46032</v>
       </c>
@@ -12600,7 +12603,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="4">
         <v>46032</v>
       </c>
@@ -12619,7 +12622,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B10" s="33">
+      <c r="B10" s="34">
         <f>SUM(E10:E11)</f>
         <v>130</v>
       </c>
@@ -12641,7 +12644,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="4">
         <v>46033</v>
       </c>
@@ -12660,7 +12663,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>SUM(E12:E14)</f>
         <v>120</v>
       </c>
@@ -12682,7 +12685,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B13" s="34"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="4">
         <v>46034</v>
       </c>
@@ -12701,7 +12704,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B14" s="34"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="4">
         <v>46034</v>
       </c>
@@ -12720,7 +12723,7 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>SUM(E15:E16)</f>
         <v>160</v>
       </c>
@@ -12742,7 +12745,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B16" s="34"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="4">
         <v>46035</v>
       </c>
@@ -12761,7 +12764,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B17" s="33">
+      <c r="B17" s="34">
         <f>SUM(E17:E18)</f>
         <v>160</v>
       </c>
@@ -12783,7 +12786,7 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B18" s="35"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="4">
         <v>46036</v>
       </c>
@@ -12802,7 +12805,7 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B19" s="33">
+      <c r="B19" s="34">
         <f>SUM(E19:E23)</f>
         <v>295</v>
       </c>
@@ -12824,7 +12827,7 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B20" s="34"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="4">
         <v>46037</v>
       </c>
@@ -12843,7 +12846,7 @@
       </c>
     </row>
     <row r="21" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B21" s="34"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="4">
         <v>46037</v>
       </c>
@@ -12856,7 +12859,7 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B22" s="34"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="4">
         <v>46037</v>
       </c>
@@ -12869,7 +12872,7 @@
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B23" s="35"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="4">
         <v>46037</v>
       </c>
@@ -12888,7 +12891,7 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B24" s="34">
+      <c r="B24" s="35">
         <f>SUM(E24:E26)</f>
         <v>140</v>
       </c>
@@ -12910,7 +12913,7 @@
       </c>
     </row>
     <row r="25" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="4">
         <v>46038</v>
       </c>
@@ -12929,7 +12932,7 @@
       </c>
     </row>
     <row r="26" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B26" s="34"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="4">
         <v>46038</v>
       </c>
@@ -12948,7 +12951,7 @@
       </c>
     </row>
     <row r="27" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B27" s="33">
+      <c r="B27" s="34">
         <f>SUM(E27:E32)</f>
         <v>370</v>
       </c>
@@ -12970,7 +12973,7 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B28" s="34"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="4">
         <v>46039</v>
       </c>
@@ -12989,7 +12992,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="4">
         <v>46039</v>
       </c>
@@ -13005,7 +13008,7 @@
       </c>
     </row>
     <row r="30" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B30" s="34"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="4">
         <v>46039</v>
       </c>
@@ -13018,7 +13021,7 @@
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="2:8" ht="22.5" customHeight="1">
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4">
         <v>46039</v>
       </c>
@@ -13031,7 +13034,7 @@
       <c r="F31" s="17"/>
     </row>
     <row r="32" spans="2:8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4">
         <v>46039</v>
       </c>
@@ -13044,7 +13047,7 @@
       <c r="F32" s="17"/>
     </row>
     <row r="33" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B33" s="33">
+      <c r="B33" s="34">
         <f>SUM(E33:E36)</f>
         <v>450</v>
       </c>
@@ -13060,7 +13063,7 @@
       <c r="F33" s="17"/>
     </row>
     <row r="34" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="4">
         <v>46040</v>
       </c>
@@ -13073,7 +13076,7 @@
       <c r="F34" s="17"/>
     </row>
     <row r="35" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="4">
         <v>46040</v>
       </c>
@@ -13086,7 +13089,7 @@
       <c r="F35" s="17"/>
     </row>
     <row r="36" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4">
         <v>46040</v>
       </c>
@@ -13099,7 +13102,7 @@
       <c r="F36" s="17"/>
     </row>
     <row r="37" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B37" s="33">
+      <c r="B37" s="34">
         <f>SUM(E37:E41)</f>
         <v>280</v>
       </c>
@@ -13115,7 +13118,7 @@
       <c r="F37" s="17"/>
     </row>
     <row r="38" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B38" s="34"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="4">
         <v>46041</v>
       </c>
@@ -13128,7 +13131,7 @@
       <c r="F38" s="17"/>
     </row>
     <row r="39" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B39" s="34"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="4">
         <v>46041</v>
       </c>
@@ -13141,7 +13144,7 @@
       <c r="F39" s="17"/>
     </row>
     <row r="40" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B40" s="34"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="4">
         <v>46041</v>
       </c>
@@ -13154,7 +13157,7 @@
       <c r="F40" s="17"/>
     </row>
     <row r="41" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B41" s="35"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="4">
         <v>46041</v>
       </c>
@@ -13183,7 +13186,7 @@
       <c r="F42" s="17"/>
     </row>
     <row r="43" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B43" s="33">
+      <c r="B43" s="34">
         <f>SUM(E43:E45)</f>
         <v>160</v>
       </c>
@@ -13199,7 +13202,7 @@
       <c r="F43" s="17"/>
     </row>
     <row r="44" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B44" s="34"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="4">
         <v>46043</v>
       </c>
@@ -13212,7 +13215,7 @@
       <c r="F44" s="17"/>
     </row>
     <row r="45" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B45" s="35"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="4">
         <v>46043</v>
       </c>
@@ -13224,9 +13227,9 @@
       </c>
       <c r="F45" s="17"/>
     </row>
-    <row r="46" spans="2:6" ht="22.5" customHeight="1">
+    <row r="46" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
       <c r="B46" s="33">
-        <f>SUM(E46:E51)</f>
+        <f>SUM(E46:E46)</f>
         <v>100</v>
       </c>
       <c r="C46" s="4">
@@ -13241,90 +13244,129 @@
       <c r="F46" s="17"/>
     </row>
     <row r="47" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B47" s="34"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
+      <c r="B47" s="34">
+        <f>SUM(E47:E49)</f>
+        <v>160</v>
+      </c>
+      <c r="C47" s="4">
+        <v>46045</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="12">
+        <v>30</v>
+      </c>
       <c r="F47" s="17"/>
     </row>
     <row r="48" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B48" s="34"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="4">
+        <v>46045</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="12">
+        <v>100</v>
+      </c>
       <c r="F48" s="17"/>
     </row>
-    <row r="49" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B49" s="34"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
+    <row r="49" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B49" s="35"/>
+      <c r="C49" s="4">
+        <v>46045</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="12">
+        <v>30</v>
+      </c>
       <c r="F49" s="17"/>
     </row>
     <row r="50" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B50" s="34"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
+      <c r="B50" s="34">
+        <f>SUM(E50:E53)</f>
+        <v>210</v>
+      </c>
+      <c r="C50" s="4">
+        <v>46046</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="12">
+        <v>150</v>
+      </c>
       <c r="F50" s="17"/>
     </row>
-    <row r="51" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+    <row r="51" spans="2:6" ht="22.5" customHeight="1">
       <c r="B51" s="35"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
+      <c r="C51" s="4">
+        <v>46046</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="12">
+        <v>30</v>
+      </c>
       <c r="F51" s="17"/>
     </row>
     <row r="52" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B52" s="33">
-        <f>SUM(E52:E55)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="4">
+        <v>46046</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="12">
+        <v>30</v>
+      </c>
       <c r="F52" s="17"/>
     </row>
-    <row r="53" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B53" s="34"/>
+    <row r="53" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B53" s="35"/>
       <c r="C53" s="4"/>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
       <c r="F53" s="17"/>
     </row>
     <row r="54" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B54" s="34"/>
+      <c r="B54" s="34">
+        <f>SUM(E54:E57)</f>
+        <v>0</v>
+      </c>
       <c r="C54" s="4"/>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
       <c r="F54" s="17"/>
     </row>
-    <row r="55" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B55" s="34"/>
+    <row r="55" spans="2:6" ht="22.5" customHeight="1">
+      <c r="B55" s="35"/>
       <c r="C55" s="4"/>
       <c r="D55" s="12"/>
       <c r="E55" s="12"/>
       <c r="F55" s="17"/>
     </row>
     <row r="56" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B56" s="33">
-        <f>SUM(E56:E57)</f>
-        <v>0</v>
-      </c>
+      <c r="B56" s="35"/>
       <c r="C56" s="4"/>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
       <c r="F56" s="17"/>
     </row>
     <row r="57" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B57" s="34"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="4"/>
       <c r="D57" s="12"/>
       <c r="E57" s="12"/>
       <c r="F57" s="17"/>
     </row>
     <row r="58" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B58" s="33">
+      <c r="B58" s="34">
         <f>SUM(E58:E61)</f>
         <v>0</v>
       </c>
@@ -13334,14 +13376,14 @@
       <c r="F58" s="17"/>
     </row>
     <row r="59" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B59" s="34"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="4"/>
       <c r="D59" s="12"/>
       <c r="E59" s="12"/>
       <c r="F59" s="17"/>
     </row>
     <row r="60" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B60" s="34"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="4"/>
       <c r="D60" s="12"/>
       <c r="E60" s="12"/>
@@ -13354,9 +13396,9 @@
       <c r="E61" s="12"/>
       <c r="F61" s="17"/>
     </row>
-    <row r="62" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B62" s="33">
-        <f>SUM(E62:E65)</f>
+    <row r="62" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B62" s="32">
+        <f>SUM(E62:E62)</f>
         <v>0</v>
       </c>
       <c r="C62" s="4"/>
@@ -13365,29 +13407,32 @@
       <c r="F62" s="17"/>
     </row>
     <row r="63" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B63" s="34"/>
+      <c r="B63" s="34">
+        <f>SUM(E63:E65)</f>
+        <v>0</v>
+      </c>
       <c r="C63" s="4"/>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
       <c r="F63" s="17"/>
     </row>
     <row r="64" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B64" s="34"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="4"/>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
       <c r="F64" s="17"/>
     </row>
     <row r="65" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B65" s="34"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="4"/>
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
       <c r="F65" s="17"/>
     </row>
-    <row r="66" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B66" s="32">
-        <f>SUM(E66:E66)</f>
+    <row r="66" spans="1:6" ht="22.5" customHeight="1">
+      <c r="B66" s="34">
+        <f>SUM(E66:E70)</f>
         <v>0</v>
       </c>
       <c r="C66" s="4"/>
@@ -13396,61 +13441,64 @@
       <c r="F66" s="17"/>
     </row>
     <row r="67" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B67" s="33">
-        <f>SUM(E67:E69)</f>
-        <v>0</v>
-      </c>
+      <c r="B67" s="35"/>
       <c r="C67" s="4"/>
       <c r="D67" s="12"/>
       <c r="E67" s="12"/>
       <c r="F67" s="17"/>
     </row>
     <row r="68" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B68" s="34"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="4"/>
       <c r="D68" s="12"/>
       <c r="E68" s="12"/>
       <c r="F68" s="17"/>
     </row>
-    <row r="69" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B69" s="34"/>
+    <row r="69" spans="1:6" ht="22.5" customHeight="1">
+      <c r="B69" s="35"/>
       <c r="C69" s="4"/>
       <c r="D69" s="12"/>
       <c r="E69" s="12"/>
       <c r="F69" s="17"/>
     </row>
-    <row r="70" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B70" s="33">
-        <f>SUM(E70:E74)</f>
-        <v>0</v>
-      </c>
+    <row r="70" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B70" s="36"/>
       <c r="C70" s="4"/>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="17"/>
     </row>
     <row r="71" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B71" s="34"/>
+      <c r="B71" s="34">
+        <f>SUM(E71:E72)</f>
+        <v>0</v>
+      </c>
       <c r="C71" s="4"/>
       <c r="D71" s="12"/>
       <c r="E71" s="12"/>
       <c r="F71" s="17"/>
     </row>
-    <row r="72" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B72" s="34"/>
+    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="A72" s="2">
+        <v>4371</v>
+      </c>
+      <c r="B72" s="35"/>
       <c r="C72" s="4"/>
       <c r="D72" s="12"/>
       <c r="E72" s="12"/>
       <c r="F72" s="17"/>
     </row>
     <row r="73" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B73" s="34"/>
+      <c r="B73" s="34">
+        <f>SUM(E73:E77)</f>
+        <v>0</v>
+      </c>
       <c r="C73" s="4"/>
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
       <c r="F73" s="17"/>
     </row>
-    <row r="74" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
+    <row r="74" spans="1:6" ht="22.5" customHeight="1">
       <c r="B74" s="35"/>
       <c r="C74" s="4"/>
       <c r="D74" s="12"/>
@@ -13458,125 +13506,122 @@
       <c r="F74" s="17"/>
     </row>
     <row r="75" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B75" s="33">
-        <f>SUM(E75:E76)</f>
-        <v>0</v>
-      </c>
+      <c r="B75" s="35"/>
       <c r="C75" s="4"/>
       <c r="D75" s="12"/>
       <c r="E75" s="12"/>
       <c r="F75" s="17"/>
     </row>
-    <row r="76" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A76" s="2">
-        <v>4371</v>
-      </c>
-      <c r="B76" s="34"/>
+    <row r="76" spans="1:6" ht="22.5" customHeight="1">
+      <c r="B76" s="35"/>
       <c r="C76" s="4"/>
       <c r="D76" s="12"/>
       <c r="E76" s="12"/>
       <c r="F76" s="17"/>
     </row>
-    <row r="77" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B77" s="33">
-        <f>SUM(E77:E81)</f>
-        <v>0</v>
-      </c>
+    <row r="77" spans="1:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B77" s="35"/>
       <c r="C77" s="4"/>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B78" s="34"/>
+      <c r="B78" s="34">
+        <f>SUM(E78:E85)</f>
+        <v>0</v>
+      </c>
       <c r="C78" s="4"/>
       <c r="D78" s="12"/>
       <c r="E78" s="12"/>
       <c r="F78" s="17"/>
     </row>
     <row r="79" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B79" s="34"/>
+      <c r="B79" s="35"/>
       <c r="C79" s="4"/>
       <c r="D79" s="12"/>
       <c r="E79" s="12"/>
       <c r="F79" s="17"/>
     </row>
     <row r="80" spans="1:6" ht="22.5" customHeight="1">
-      <c r="B80" s="34"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="4"/>
       <c r="D80" s="12"/>
       <c r="E80" s="12"/>
       <c r="F80" s="17"/>
     </row>
-    <row r="81" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B81" s="34"/>
+    <row r="81" spans="2:6" ht="22.5" customHeight="1">
+      <c r="B81" s="35"/>
       <c r="C81" s="4"/>
       <c r="D81" s="12"/>
       <c r="E81" s="12"/>
       <c r="F81" s="17"/>
     </row>
     <row r="82" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B82" s="33">
-        <f>SUM(E82:E89)</f>
-        <v>0</v>
-      </c>
+      <c r="B82" s="35"/>
       <c r="C82" s="4"/>
       <c r="D82" s="12"/>
       <c r="E82" s="12"/>
       <c r="F82" s="17"/>
     </row>
     <row r="83" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="4"/>
       <c r="D83" s="12"/>
       <c r="E83" s="12"/>
       <c r="F83" s="17"/>
     </row>
     <row r="84" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="4"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
       <c r="F84" s="17"/>
     </row>
-    <row r="85" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B85" s="34"/>
+    <row r="85" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B85" s="35"/>
       <c r="C85" s="4"/>
       <c r="D85" s="12"/>
       <c r="E85" s="12"/>
       <c r="F85" s="17"/>
     </row>
-    <row r="86" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B86" s="34"/>
+    <row r="86" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B86" s="32">
+        <f>SUM(E86:E86)</f>
+        <v>0</v>
+      </c>
       <c r="C86" s="4"/>
       <c r="D86" s="12"/>
       <c r="E86" s="12"/>
       <c r="F86" s="17"/>
     </row>
     <row r="87" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B87" s="34"/>
+      <c r="B87" s="34">
+        <f>SUM(E87:E89)</f>
+        <v>0</v>
+      </c>
       <c r="C87" s="4"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="17"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="19"/>
     </row>
     <row r="88" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B88" s="34"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="17"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="19"/>
     </row>
     <row r="89" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B89" s="34"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
       <c r="F89" s="17"/>
     </row>
-    <row r="90" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B90" s="32">
-        <f>SUM(E90:E90)</f>
+    <row r="90" spans="2:6" ht="22.5" customHeight="1">
+      <c r="B90" s="34">
+        <f>SUM(E90:E92)</f>
         <v>0</v>
       </c>
       <c r="C90" s="4"/>
@@ -13585,47 +13630,44 @@
       <c r="F90" s="17"/>
     </row>
     <row r="91" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B91" s="33">
-        <f>SUM(E91:E93)</f>
+      <c r="B91" s="35"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="17"/>
+    </row>
+    <row r="92" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+      <c r="B92" s="36"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="17"/>
+    </row>
+    <row r="93" spans="2:6" ht="22.5" customHeight="1">
+      <c r="B93" s="34">
+        <f>SUM(E93:E94)</f>
         <v>0</v>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="19"/>
-    </row>
-    <row r="92" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B92" s="34"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="19"/>
-    </row>
-    <row r="93" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B93" s="34"/>
       <c r="C93" s="4"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
       <c r="F93" s="17"/>
     </row>
     <row r="94" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B94" s="33">
-        <f>SUM(E94:E96)</f>
-        <v>0</v>
-      </c>
+      <c r="B94" s="35"/>
       <c r="C94" s="4"/>
       <c r="D94" s="12"/>
       <c r="E94" s="12"/>
       <c r="F94" s="17"/>
     </row>
     <row r="95" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B95" s="34"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="4"/>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
       <c r="F95" s="17"/>
     </row>
-    <row r="96" spans="2:6" ht="22.5" customHeight="1" thickBot="1">
+    <row r="96" spans="2:6" ht="22.5" customHeight="1">
       <c r="B96" s="35"/>
       <c r="C96" s="4"/>
       <c r="D96" s="12"/>
@@ -13633,68 +13675,41 @@
       <c r="F96" s="17"/>
     </row>
     <row r="97" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B97" s="33">
+      <c r="B97" s="44">
         <f>SUM(E97:E98)</f>
         <v>0</v>
       </c>
       <c r="C97" s="4"/>
-      <c r="D97" s="12"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="17"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="19"/>
     </row>
     <row r="98" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B98" s="34"/>
+      <c r="B98" s="45"/>
       <c r="C98" s="4"/>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
       <c r="F98" s="17"/>
     </row>
     <row r="99" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B99" s="34"/>
       <c r="C99" s="4"/>
       <c r="D99" s="12"/>
       <c r="E99" s="12"/>
       <c r="F99" s="17"/>
     </row>
-    <row r="100" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B100" s="34"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="12"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="17"/>
-    </row>
-    <row r="101" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B101" s="43">
-        <f>SUM(E101:E102)</f>
-        <v>0</v>
-      </c>
-      <c r="C101" s="4"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="19"/>
-    </row>
-    <row r="102" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B102" s="44"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="17"/>
-    </row>
-    <row r="103" spans="2:6" ht="22.5" customHeight="1">
-      <c r="C103" s="4"/>
-      <c r="D103" s="12"/>
-      <c r="E103" s="12"/>
-      <c r="F103" s="17"/>
-    </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B11"/>
+  <mergeCells count="27">
+    <mergeCell ref="B87:B89"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="B97:B98"/>
     <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B70"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="B73:B77"/>
+    <mergeCell ref="B78:B85"/>
+    <mergeCell ref="B54:B57"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="B19:B23"/>
@@ -13702,20 +13717,15 @@
     <mergeCell ref="B33:B36"/>
     <mergeCell ref="B37:B41"/>
     <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B51"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B50:B53"/>
     <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B82:B89"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:E14 E46:E1048576 E16:E44">
     <cfRule type="cellIs" dxfId="3" priority="7" operator="between">
